--- a/Dados/table_PROD_RS_ANUAL_1_aux.xlsx
+++ b/Dados/table_PROD_RS_ANUAL_1_aux.xlsx
@@ -11,12 +11,18 @@
     <sheet name="n" sheetId="2" r:id="rId2"/>
     <sheet name="hb" sheetId="3" r:id="rId3"/>
     <sheet name="ef" sheetId="4" r:id="rId4"/>
-    <sheet name="n_p_cv" sheetId="5" r:id="rId5"/>
-    <sheet name="hb_p_cv" sheetId="6" r:id="rId6"/>
-    <sheet name="ef_p_cv" sheetId="7" r:id="rId7"/>
-    <sheet name="n_s_cv" sheetId="8" r:id="rId8"/>
-    <sheet name="hb_s_cv" sheetId="9" r:id="rId9"/>
-    <sheet name="ef_s_cv" sheetId="10" r:id="rId10"/>
+    <sheet name="n_p" sheetId="5" r:id="rId5"/>
+    <sheet name="hb_p" sheetId="6" r:id="rId6"/>
+    <sheet name="ef_p" sheetId="7" r:id="rId7"/>
+    <sheet name="n_s" sheetId="8" r:id="rId8"/>
+    <sheet name="hb_s" sheetId="9" r:id="rId9"/>
+    <sheet name="ef_s" sheetId="10" r:id="rId10"/>
+    <sheet name="n_p_cv" sheetId="11" r:id="rId11"/>
+    <sheet name="hb_p_cv" sheetId="12" r:id="rId12"/>
+    <sheet name="ef_p_cv" sheetId="13" r:id="rId13"/>
+    <sheet name="n_s_cv" sheetId="14" r:id="rId14"/>
+    <sheet name="hb_s_cv" sheetId="15" r:id="rId15"/>
+    <sheet name="ef_s_cv" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1249,6 +1255,3927 @@
         </is>
       </c>
       <c r="B2">
+        <v>583814.81168922</v>
+      </c>
+      <c r="C2">
+        <v>10721.39398632</v>
+      </c>
+      <c r="D2">
+        <v>216417.58135496</v>
+      </c>
+      <c r="E2">
+        <v>15978.66760238</v>
+      </c>
+      <c r="F2">
+        <v>138984.10384426</v>
+      </c>
+      <c r="G2">
+        <v>299072.96838004</v>
+      </c>
+      <c r="H2">
+        <v>112800.00907481</v>
+      </c>
+      <c r="I2">
+        <v>60164.93199269</v>
+      </c>
+      <c r="J2">
+        <v>8678.53267692</v>
+      </c>
+      <c r="K2">
+        <v>25578.8187439</v>
+      </c>
+      <c r="L2">
+        <v>1293831.47751996</v>
+      </c>
+      <c r="M2">
+        <v>787519.43209632</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>643494.82347909</v>
+      </c>
+      <c r="C3">
+        <v>6379.15036752</v>
+      </c>
+      <c r="D3">
+        <v>201229.66771184</v>
+      </c>
+      <c r="F3">
+        <v>153640.47470018</v>
+      </c>
+      <c r="G3">
+        <v>288280.0130007</v>
+      </c>
+      <c r="H3">
+        <v>127051.00913345</v>
+      </c>
+      <c r="I3">
+        <v>58894.71622678</v>
+      </c>
+      <c r="J3">
+        <v>21249.1742966</v>
+      </c>
+      <c r="K3">
+        <v>47587.546159</v>
+      </c>
+      <c r="L3">
+        <v>1569307.02241102</v>
+      </c>
+      <c r="M3">
+        <v>826940.00866107</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>607851.90474387</v>
+      </c>
+      <c r="C4">
+        <v>2780.50693607</v>
+      </c>
+      <c r="D4">
+        <v>208288.18331371</v>
+      </c>
+      <c r="F4">
+        <v>216850.79772527</v>
+      </c>
+      <c r="G4">
+        <v>402309.80853225</v>
+      </c>
+      <c r="H4">
+        <v>129738.43667691</v>
+      </c>
+      <c r="I4">
+        <v>45228.83770787</v>
+      </c>
+      <c r="J4">
+        <v>6790.762949739999</v>
+      </c>
+      <c r="K4">
+        <v>55523.1044049</v>
+      </c>
+      <c r="L4">
+        <v>1537082.77645996</v>
+      </c>
+      <c r="M4">
+        <v>754598.96632687</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>680525.1910028399</v>
+      </c>
+      <c r="D5">
+        <v>201709.14360692</v>
+      </c>
+      <c r="F5">
+        <v>101349.53122512</v>
+      </c>
+      <c r="G5">
+        <v>468526.3967978</v>
+      </c>
+      <c r="H5">
+        <v>119606.15781099</v>
+      </c>
+      <c r="I5">
+        <v>13833.60064455</v>
+      </c>
+      <c r="J5">
+        <v>13161.09105555</v>
+      </c>
+      <c r="K5">
+        <v>3641.4020217</v>
+      </c>
+      <c r="L5">
+        <v>1438198.0414195</v>
+      </c>
+      <c r="M5">
+        <v>862453.5656565099</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>685716.5898272</v>
+      </c>
+      <c r="D6">
+        <v>183749.28406113</v>
+      </c>
+      <c r="E6">
+        <v>6359.79873984</v>
+      </c>
+      <c r="F6">
+        <v>43329.64727679</v>
+      </c>
+      <c r="G6">
+        <v>292240.5410903</v>
+      </c>
+      <c r="H6">
+        <v>170327.48062912</v>
+      </c>
+      <c r="I6">
+        <v>20441.4733226</v>
+      </c>
+      <c r="J6">
+        <v>3378.70620944</v>
+      </c>
+      <c r="K6">
+        <v>8996.764264450001</v>
+      </c>
+      <c r="L6">
+        <v>1205030.43579473</v>
+      </c>
+      <c r="M6">
+        <v>760114.3135363901</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1006701.75150813</v>
+      </c>
+      <c r="D7">
+        <v>106941.06526063</v>
+      </c>
+      <c r="F7">
+        <v>119641.02562997</v>
+      </c>
+      <c r="G7">
+        <v>310901.41894156</v>
+      </c>
+      <c r="H7">
+        <v>206923.27417051</v>
+      </c>
+      <c r="I7">
+        <v>35020.50383218</v>
+      </c>
+      <c r="J7">
+        <v>3425.3936989</v>
+      </c>
+      <c r="K7">
+        <v>38096.68472073</v>
+      </c>
+      <c r="L7">
+        <v>1495157.22970122</v>
+      </c>
+      <c r="M7">
+        <v>703485.09210506</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>922225.23289676</v>
+      </c>
+      <c r="D8">
+        <v>229146.10883338</v>
+      </c>
+      <c r="E8">
+        <v>6979.60466304</v>
+      </c>
+      <c r="F8">
+        <v>167684.48656045</v>
+      </c>
+      <c r="G8">
+        <v>495178.28649823</v>
+      </c>
+      <c r="H8">
+        <v>168251.84747807</v>
+      </c>
+      <c r="I8">
+        <v>30452.24189459</v>
+      </c>
+      <c r="J8">
+        <v>4066.7076715</v>
+      </c>
+      <c r="K8">
+        <v>18383.9978713</v>
+      </c>
+      <c r="L8">
+        <v>1405201.93606059</v>
+      </c>
+      <c r="M8">
+        <v>619014.1840727601</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>876964.77008589</v>
+      </c>
+      <c r="C9">
+        <v>1709.0309305</v>
+      </c>
+      <c r="D9">
+        <v>169780.48876886</v>
+      </c>
+      <c r="F9">
+        <v>94508.41933749001</v>
+      </c>
+      <c r="G9">
+        <v>409351.67970699</v>
+      </c>
+      <c r="H9">
+        <v>125886.74184034</v>
+      </c>
+      <c r="I9">
+        <v>40033.3017117</v>
+      </c>
+      <c r="J9">
+        <v>31296.12663786</v>
+      </c>
+      <c r="K9">
+        <v>25166.0217987</v>
+      </c>
+      <c r="L9">
+        <v>1562965.88992476</v>
+      </c>
+      <c r="M9">
+        <v>605475.6215637</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>760117.36201863</v>
+      </c>
+      <c r="D10">
+        <v>63854.48843452</v>
+      </c>
+      <c r="F10">
+        <v>49699.47982741</v>
+      </c>
+      <c r="G10">
+        <v>199040.33616225</v>
+      </c>
+      <c r="H10">
+        <v>29402.48970306</v>
+      </c>
+      <c r="I10">
+        <v>61572.62392021</v>
+      </c>
+      <c r="J10">
+        <v>5971.0621158</v>
+      </c>
+      <c r="K10">
+        <v>15014.322301</v>
+      </c>
+      <c r="L10">
+        <v>1018673.07453573</v>
+      </c>
+      <c r="M10">
+        <v>560986.2057704501</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>413119.50338783</v>
+      </c>
+      <c r="C11">
+        <v>9153.413098200001</v>
+      </c>
+      <c r="D11">
+        <v>96862.16337567</v>
+      </c>
+      <c r="F11">
+        <v>79974.19949494</v>
+      </c>
+      <c r="G11">
+        <v>472837.92475486</v>
+      </c>
+      <c r="H11">
+        <v>60623.62806593</v>
+      </c>
+      <c r="I11">
+        <v>72477.73591592</v>
+      </c>
+      <c r="J11">
+        <v>6711.7199208</v>
+      </c>
+      <c r="K11">
+        <v>8413.024689280001</v>
+      </c>
+      <c r="L11">
+        <v>933615.11314736</v>
+      </c>
+      <c r="M11">
+        <v>576019.5614699</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>600137.4902832099</v>
+      </c>
+      <c r="C12">
+        <v>4717.95226911</v>
+      </c>
+      <c r="D12">
+        <v>135710.79162629</v>
+      </c>
+      <c r="F12">
+        <v>61891.03584894</v>
+      </c>
+      <c r="G12">
+        <v>371432.54265078</v>
+      </c>
+      <c r="H12">
+        <v>112199.56714415</v>
+      </c>
+      <c r="I12">
+        <v>95130.37878756999</v>
+      </c>
+      <c r="J12">
+        <v>21227.34482008</v>
+      </c>
+      <c r="K12">
+        <v>50575.2773875</v>
+      </c>
+      <c r="L12">
+        <v>1164824.36090757</v>
+      </c>
+      <c r="M12">
+        <v>643933.65687156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>584149.0743460701</v>
+      </c>
+      <c r="D13">
+        <v>167017.26489313</v>
+      </c>
+      <c r="E13">
+        <v>13116.4635492</v>
+      </c>
+      <c r="F13">
+        <v>90942.35883608001</v>
+      </c>
+      <c r="G13">
+        <v>336324.27213147</v>
+      </c>
+      <c r="H13">
+        <v>208331.46685906</v>
+      </c>
+      <c r="I13">
+        <v>106205.58981997</v>
+      </c>
+      <c r="J13">
+        <v>67908.35641492999</v>
+      </c>
+      <c r="K13">
+        <v>5157.5317434</v>
+      </c>
+      <c r="L13">
+        <v>1720442.723001</v>
+      </c>
+      <c r="M13">
+        <v>583573.66931905</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>580871.43786482</v>
+      </c>
+      <c r="D14">
+        <v>227480.23274883</v>
+      </c>
+      <c r="E14">
+        <v>11263.33294488</v>
+      </c>
+      <c r="F14">
+        <v>109199.70932221</v>
+      </c>
+      <c r="G14">
+        <v>545562.1525235299</v>
+      </c>
+      <c r="H14">
+        <v>233204.15654568</v>
+      </c>
+      <c r="I14">
+        <v>138080.62127203</v>
+      </c>
+      <c r="J14">
+        <v>75246.25260681</v>
+      </c>
+      <c r="K14">
+        <v>38053.28388012</v>
+      </c>
+      <c r="L14">
+        <v>1818599.23634789</v>
+      </c>
+      <c r="M14">
+        <v>631100.4219671</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>1650772.71585219</v>
+      </c>
+      <c r="D15">
+        <v>455009.12749454</v>
+      </c>
+      <c r="F15">
+        <v>320470.3431503</v>
+      </c>
+      <c r="G15">
+        <v>1139583.46453642</v>
+      </c>
+      <c r="H15">
+        <v>553482.05657221</v>
+      </c>
+      <c r="I15">
+        <v>261651.78679219</v>
+      </c>
+      <c r="J15">
+        <v>36522.58701203</v>
+      </c>
+      <c r="K15">
+        <v>153615.1244399</v>
+      </c>
+      <c r="L15">
+        <v>5444851.9039135</v>
+      </c>
+      <c r="M15">
+        <v>2175313.80843183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4.259314026947806</v>
+      </c>
+      <c r="C2">
+        <v>24.77470931554573</v>
+      </c>
+      <c r="D2">
+        <v>4.233987073791424</v>
+      </c>
+      <c r="E2">
+        <v>13.00466104342871</v>
+      </c>
+      <c r="F2">
+        <v>4.581394321289869</v>
+      </c>
+      <c r="G2">
+        <v>2.953079986300894</v>
+      </c>
+      <c r="H2">
+        <v>4.671119521597542</v>
+      </c>
+      <c r="I2">
+        <v>9.217611801967001</v>
+      </c>
+      <c r="J2">
+        <v>9.331425489773185</v>
+      </c>
+      <c r="K2">
+        <v>13.89229222252481</v>
+      </c>
+      <c r="L2">
+        <v>2.471244029523893</v>
+      </c>
+      <c r="M2">
+        <v>4.121800638579302</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>4.759075829736644</v>
+      </c>
+      <c r="C3">
+        <v>26.06594324618619</v>
+      </c>
+      <c r="D3">
+        <v>3.804791787181957</v>
+      </c>
+      <c r="E3">
+        <v>12.52622823104816</v>
+      </c>
+      <c r="F3">
+        <v>4.150578462442391</v>
+      </c>
+      <c r="G3">
+        <v>2.896456042208567</v>
+      </c>
+      <c r="H3">
+        <v>5.013962143736643</v>
+      </c>
+      <c r="I3">
+        <v>10.85672283777362</v>
+      </c>
+      <c r="J3">
+        <v>9.476012462596222</v>
+      </c>
+      <c r="K3">
+        <v>12.69626750469292</v>
+      </c>
+      <c r="L3">
+        <v>2.201877131160674</v>
+      </c>
+      <c r="M3">
+        <v>4.167940872353753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3.90155814828158</v>
+      </c>
+      <c r="C4">
+        <v>29.18032049398214</v>
+      </c>
+      <c r="D4">
+        <v>4.23978296948431</v>
+      </c>
+      <c r="E4">
+        <v>12.51123935952304</v>
+      </c>
+      <c r="F4">
+        <v>4.679322271809349</v>
+      </c>
+      <c r="G4">
+        <v>2.81247070045096</v>
+      </c>
+      <c r="H4">
+        <v>4.966215972095638</v>
+      </c>
+      <c r="I4">
+        <v>9.301496960665185</v>
+      </c>
+      <c r="J4">
+        <v>11.27801205222521</v>
+      </c>
+      <c r="K4">
+        <v>15.30473086234856</v>
+      </c>
+      <c r="L4">
+        <v>2.121379036943623</v>
+      </c>
+      <c r="M4">
+        <v>3.962916853970821</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4.387626588180623</v>
+      </c>
+      <c r="C5">
+        <v>26.70011505543284</v>
+      </c>
+      <c r="D5">
+        <v>3.676040446678344</v>
+      </c>
+      <c r="E5">
+        <v>11.19876597441593</v>
+      </c>
+      <c r="F5">
+        <v>4.790987906238347</v>
+      </c>
+      <c r="G5">
+        <v>3.041386590180601</v>
+      </c>
+      <c r="H5">
+        <v>5.629516204470749</v>
+      </c>
+      <c r="I5">
+        <v>11.1539533800914</v>
+      </c>
+      <c r="J5">
+        <v>9.705942095983612</v>
+      </c>
+      <c r="K5">
+        <v>16.99644740997108</v>
+      </c>
+      <c r="L5">
+        <v>2.038840897899551</v>
+      </c>
+      <c r="M5">
+        <v>4.347967509808808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>5.402289780333358</v>
+      </c>
+      <c r="C6">
+        <v>34.50268205265301</v>
+      </c>
+      <c r="D6">
+        <v>3.730003146176953</v>
+      </c>
+      <c r="E6">
+        <v>14.34179298117949</v>
+      </c>
+      <c r="F6">
+        <v>4.701181243961572</v>
+      </c>
+      <c r="G6">
+        <v>3.13456539616592</v>
+      </c>
+      <c r="H6">
+        <v>5.629128655789447</v>
+      </c>
+      <c r="I6">
+        <v>10.57997719040547</v>
+      </c>
+      <c r="J6">
+        <v>8.936858289700391</v>
+      </c>
+      <c r="K6">
+        <v>13.88176819551973</v>
+      </c>
+      <c r="L6">
+        <v>2.448945496977677</v>
+      </c>
+      <c r="M6">
+        <v>4.147572196881462</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5.093865264787558</v>
+      </c>
+      <c r="C7">
+        <v>33.84236474066733</v>
+      </c>
+      <c r="D7">
+        <v>3.907918265021192</v>
+      </c>
+      <c r="E7">
+        <v>12.61250180233113</v>
+      </c>
+      <c r="F7">
+        <v>4.742511424159299</v>
+      </c>
+      <c r="G7">
+        <v>2.859763738786211</v>
+      </c>
+      <c r="H7">
+        <v>5.402766004342859</v>
+      </c>
+      <c r="I7">
+        <v>11.14743336512764</v>
+      </c>
+      <c r="J7">
+        <v>8.950081543412857</v>
+      </c>
+      <c r="K7">
+        <v>12.7540877214365</v>
+      </c>
+      <c r="L7">
+        <v>2.29842258155511</v>
+      </c>
+      <c r="M7">
+        <v>3.954120049889515</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5.083171597389869</v>
+      </c>
+      <c r="C8">
+        <v>33.77149497886662</v>
+      </c>
+      <c r="D8">
+        <v>4.61166714209377</v>
+      </c>
+      <c r="E8">
+        <v>15.65932139969655</v>
+      </c>
+      <c r="F8">
+        <v>5.130895826102762</v>
+      </c>
+      <c r="G8">
+        <v>3.593779973840045</v>
+      </c>
+      <c r="H8">
+        <v>5.921529570666448</v>
+      </c>
+      <c r="I8">
+        <v>12.05346454577352</v>
+      </c>
+      <c r="J8">
+        <v>11.15023119929403</v>
+      </c>
+      <c r="K8">
+        <v>13.61093766274534</v>
+      </c>
+      <c r="L8">
+        <v>2.261189669037102</v>
+      </c>
+      <c r="M8">
+        <v>3.7801759261042</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5.081410872922184</v>
+      </c>
+      <c r="C9">
+        <v>34.44190437999934</v>
+      </c>
+      <c r="D9">
+        <v>4.859230799126681</v>
+      </c>
+      <c r="E9">
+        <v>15.10003056022195</v>
+      </c>
+      <c r="F9">
+        <v>4.993846388355517</v>
+      </c>
+      <c r="G9">
+        <v>2.54655328156663</v>
+      </c>
+      <c r="H9">
+        <v>4.94993345903978</v>
+      </c>
+      <c r="I9">
+        <v>13.37758168737181</v>
+      </c>
+      <c r="J9">
+        <v>11.43894131402542</v>
+      </c>
+      <c r="K9">
+        <v>12.88453997086682</v>
+      </c>
+      <c r="L9">
+        <v>2.213187648228128</v>
+      </c>
+      <c r="M9">
+        <v>3.774710422814934</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>5.344193530294172</v>
+      </c>
+      <c r="C10">
+        <v>37.3440424891886</v>
+      </c>
+      <c r="D10">
+        <v>4.645724093281102</v>
+      </c>
+      <c r="E10">
+        <v>15.6519289050374</v>
+      </c>
+      <c r="F10">
+        <v>5.612520754812202</v>
+      </c>
+      <c r="G10">
+        <v>3.560342932784545</v>
+      </c>
+      <c r="H10">
+        <v>4.988390193044472</v>
+      </c>
+      <c r="I10">
+        <v>10.97565750278677</v>
+      </c>
+      <c r="J10">
+        <v>11.46928253163459</v>
+      </c>
+      <c r="K10">
+        <v>13.66982034775643</v>
+      </c>
+      <c r="L10">
+        <v>2.45759010942185</v>
+      </c>
+      <c r="M10">
+        <v>4.202213462967589</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>5.617328680093157</v>
+      </c>
+      <c r="C11">
+        <v>42.01097016036041</v>
+      </c>
+      <c r="D11">
+        <v>4.866108100912169</v>
+      </c>
+      <c r="E11">
+        <v>15.36073003389004</v>
+      </c>
+      <c r="F11">
+        <v>7.306480559277197</v>
+      </c>
+      <c r="G11">
+        <v>3.330571371740546</v>
+      </c>
+      <c r="H11">
+        <v>6.150036267523742</v>
+      </c>
+      <c r="I11">
+        <v>11.17801266006694</v>
+      </c>
+      <c r="J11">
+        <v>10.65372514019709</v>
+      </c>
+      <c r="K11">
+        <v>15.60645541401483</v>
+      </c>
+      <c r="L11">
+        <v>2.636713873958467</v>
+      </c>
+      <c r="M11">
+        <v>4.483120963790372</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>5.069195535210546</v>
+      </c>
+      <c r="C12">
+        <v>35.2147888792215</v>
+      </c>
+      <c r="D12">
+        <v>5.112226473547582</v>
+      </c>
+      <c r="E12">
+        <v>12.82671598742309</v>
+      </c>
+      <c r="F12">
+        <v>4.979943101935063</v>
+      </c>
+      <c r="G12">
+        <v>4.036490703831773</v>
+      </c>
+      <c r="H12">
+        <v>6.387589466178004</v>
+      </c>
+      <c r="I12">
+        <v>9.46650858416224</v>
+      </c>
+      <c r="J12">
+        <v>9.574899684079915</v>
+      </c>
+      <c r="K12">
+        <v>15.9356793561706</v>
+      </c>
+      <c r="L12">
+        <v>2.600483862408256</v>
+      </c>
+      <c r="M12">
+        <v>5.068821687777465</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5.388413137518194</v>
+      </c>
+      <c r="C13">
+        <v>65.75590486628836</v>
+      </c>
+      <c r="D13">
+        <v>5.191104338740229</v>
+      </c>
+      <c r="E13">
+        <v>15.61280053543057</v>
+      </c>
+      <c r="F13">
+        <v>5.294222114664195</v>
+      </c>
+      <c r="G13">
+        <v>3.269721774267901</v>
+      </c>
+      <c r="H13">
+        <v>6.275784981294243</v>
+      </c>
+      <c r="I13">
+        <v>9.636835208035075</v>
+      </c>
+      <c r="J13">
+        <v>11.5398059414681</v>
+      </c>
+      <c r="K13">
+        <v>13.3005123097336</v>
+      </c>
+      <c r="L13">
+        <v>2.724262686460723</v>
+      </c>
+      <c r="M13">
+        <v>4.521622641837204</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>5.583402427436035</v>
+      </c>
+      <c r="C14">
+        <v>34.09210194100303</v>
+      </c>
+      <c r="D14">
+        <v>4.750967718405673</v>
+      </c>
+      <c r="E14">
+        <v>14.24498141935839</v>
+      </c>
+      <c r="F14">
+        <v>4.809642788510633</v>
+      </c>
+      <c r="G14">
+        <v>2.647734586025055</v>
+      </c>
+      <c r="H14">
+        <v>5.702971315715192</v>
+      </c>
+      <c r="I14">
+        <v>9.947187977501484</v>
+      </c>
+      <c r="J14">
+        <v>11.1427385016287</v>
+      </c>
+      <c r="K14">
+        <v>13.32893244442354</v>
+      </c>
+      <c r="L14">
+        <v>2.219495014628453</v>
+      </c>
+      <c r="M14">
+        <v>4.230148208989586</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2.801494740971123</v>
+      </c>
+      <c r="C15">
+        <v>21.42874699638312</v>
+      </c>
+      <c r="D15">
+        <v>2.579167732812248</v>
+      </c>
+      <c r="E15">
+        <v>8.839013797088045</v>
+      </c>
+      <c r="F15">
+        <v>2.50396723498876</v>
+      </c>
+      <c r="G15">
+        <v>1.345952862980189</v>
+      </c>
+      <c r="H15">
+        <v>3.187451298122609</v>
+      </c>
+      <c r="I15">
+        <v>5.250948842459695</v>
+      </c>
+      <c r="J15">
+        <v>5.047516493658409</v>
+      </c>
+      <c r="K15">
+        <v>7.34276076077593</v>
+      </c>
+      <c r="L15">
+        <v>1.2751156764505</v>
+      </c>
+      <c r="M15">
+        <v>2.218039121600745</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4.761065154235808</v>
+      </c>
+      <c r="C2">
+        <v>25.0292155012763</v>
+      </c>
+      <c r="D2">
+        <v>4.316832306864735</v>
+      </c>
+      <c r="E2">
+        <v>12.75305920803599</v>
+      </c>
+      <c r="F2">
+        <v>4.535381916647462</v>
+      </c>
+      <c r="G2">
+        <v>3.183461575993505</v>
+      </c>
+      <c r="H2">
+        <v>4.920667992943769</v>
+      </c>
+      <c r="I2">
+        <v>9.486609230584248</v>
+      </c>
+      <c r="J2">
+        <v>9.748194755269294</v>
+      </c>
+      <c r="K2">
+        <v>14.65008531581546</v>
+      </c>
+      <c r="L2">
+        <v>2.659526969323039</v>
+      </c>
+      <c r="M2">
+        <v>4.281994401053494</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>4.957182608727809</v>
+      </c>
+      <c r="C3">
+        <v>25.48704840418356</v>
+      </c>
+      <c r="D3">
+        <v>3.896687995659227</v>
+      </c>
+      <c r="E3">
+        <v>13.71775863007784</v>
+      </c>
+      <c r="F3">
+        <v>4.304315730717502</v>
+      </c>
+      <c r="G3">
+        <v>2.901481839858977</v>
+      </c>
+      <c r="H3">
+        <v>5.226533428955503</v>
+      </c>
+      <c r="I3">
+        <v>11.17785166900363</v>
+      </c>
+      <c r="J3">
+        <v>10.32294088359526</v>
+      </c>
+      <c r="K3">
+        <v>13.08765532395026</v>
+      </c>
+      <c r="L3">
+        <v>2.305669217386036</v>
+      </c>
+      <c r="M3">
+        <v>4.264477268327354</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>4.621107580910606</v>
+      </c>
+      <c r="C4">
+        <v>29.82501190121488</v>
+      </c>
+      <c r="D4">
+        <v>4.50793563802797</v>
+      </c>
+      <c r="E4">
+        <v>12.40978692334551</v>
+      </c>
+      <c r="F4">
+        <v>4.745895638570152</v>
+      </c>
+      <c r="G4">
+        <v>2.953222413533885</v>
+      </c>
+      <c r="H4">
+        <v>5.054774190695815</v>
+      </c>
+      <c r="I4">
+        <v>9.281532773677794</v>
+      </c>
+      <c r="J4">
+        <v>11.6311173598268</v>
+      </c>
+      <c r="K4">
+        <v>15.8455879951145</v>
+      </c>
+      <c r="L4">
+        <v>2.306735260317303</v>
+      </c>
+      <c r="M4">
+        <v>4.0300941484044</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4.634857059128383</v>
+      </c>
+      <c r="C5">
+        <v>26.16575446895731</v>
+      </c>
+      <c r="D5">
+        <v>3.749777259520345</v>
+      </c>
+      <c r="E5">
+        <v>11.67964185600136</v>
+      </c>
+      <c r="F5">
+        <v>4.811655836679517</v>
+      </c>
+      <c r="G5">
+        <v>3.322951907127385</v>
+      </c>
+      <c r="H5">
+        <v>5.849785552669916</v>
+      </c>
+      <c r="I5">
+        <v>11.95212818927324</v>
+      </c>
+      <c r="J5">
+        <v>9.857390207428294</v>
+      </c>
+      <c r="K5">
+        <v>17.89636076467712</v>
+      </c>
+      <c r="L5">
+        <v>2.326086332176682</v>
+      </c>
+      <c r="M5">
+        <v>4.501779466606551</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>6.021649254588031</v>
+      </c>
+      <c r="C6">
+        <v>33.412835739712</v>
+      </c>
+      <c r="D6">
+        <v>3.72400295038999</v>
+      </c>
+      <c r="E6">
+        <v>14.80178281610042</v>
+      </c>
+      <c r="F6">
+        <v>4.796872579513805</v>
+      </c>
+      <c r="G6">
+        <v>3.23921203175561</v>
+      </c>
+      <c r="H6">
+        <v>5.572714938172997</v>
+      </c>
+      <c r="I6">
+        <v>11.18458352805767</v>
+      </c>
+      <c r="J6">
+        <v>9.168635134654707</v>
+      </c>
+      <c r="K6">
+        <v>14.06630639658684</v>
+      </c>
+      <c r="L6">
+        <v>2.614133774538237</v>
+      </c>
+      <c r="M6">
+        <v>4.250965283639797</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5.200165653335199</v>
+      </c>
+      <c r="C7">
+        <v>33.47308059469479</v>
+      </c>
+      <c r="D7">
+        <v>3.979482976268262</v>
+      </c>
+      <c r="E7">
+        <v>12.88120520212823</v>
+      </c>
+      <c r="F7">
+        <v>4.778564609248476</v>
+      </c>
+      <c r="G7">
+        <v>3.032694089882847</v>
+      </c>
+      <c r="H7">
+        <v>5.494229550988178</v>
+      </c>
+      <c r="I7">
+        <v>11.13833962074656</v>
+      </c>
+      <c r="J7">
+        <v>9.272177239913857</v>
+      </c>
+      <c r="K7">
+        <v>13.52834308261482</v>
+      </c>
+      <c r="L7">
+        <v>2.471672164495317</v>
+      </c>
+      <c r="M7">
+        <v>4.019885481486879</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5.363176466552241</v>
+      </c>
+      <c r="C8">
+        <v>34.31415487961301</v>
+      </c>
+      <c r="D8">
+        <v>4.688470857966046</v>
+      </c>
+      <c r="E8">
+        <v>16.30499578044843</v>
+      </c>
+      <c r="F8">
+        <v>5.110422414366949</v>
+      </c>
+      <c r="G8">
+        <v>3.672365440152794</v>
+      </c>
+      <c r="H8">
+        <v>5.991170298906833</v>
+      </c>
+      <c r="I8">
+        <v>12.15595501221395</v>
+      </c>
+      <c r="J8">
+        <v>11.32064196217064</v>
+      </c>
+      <c r="K8">
+        <v>14.88220183526882</v>
+      </c>
+      <c r="L8">
+        <v>2.591101795331353</v>
+      </c>
+      <c r="M8">
+        <v>3.858966305049048</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5.471076149800356</v>
+      </c>
+      <c r="C9">
+        <v>34.50766685386222</v>
+      </c>
+      <c r="D9">
+        <v>4.918904336987787</v>
+      </c>
+      <c r="E9">
+        <v>15.16787587509637</v>
+      </c>
+      <c r="F9">
+        <v>5.101313480870764</v>
+      </c>
+      <c r="G9">
+        <v>2.661810339996531</v>
+      </c>
+      <c r="H9">
+        <v>5.152264143100471</v>
+      </c>
+      <c r="I9">
+        <v>13.48845287999159</v>
+      </c>
+      <c r="J9">
+        <v>11.87420527310148</v>
+      </c>
+      <c r="K9">
+        <v>13.12917169011798</v>
+      </c>
+      <c r="L9">
+        <v>2.495904177774119</v>
+      </c>
+      <c r="M9">
+        <v>3.94283415826007</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>5.587799546579201</v>
+      </c>
+      <c r="C10">
+        <v>37.30930159780443</v>
+      </c>
+      <c r="D10">
+        <v>4.792421814835913</v>
+      </c>
+      <c r="E10">
+        <v>15.8608760681409</v>
+      </c>
+      <c r="F10">
+        <v>5.757118915929259</v>
+      </c>
+      <c r="G10">
+        <v>3.695255613414222</v>
+      </c>
+      <c r="H10">
+        <v>5.301657297348373</v>
+      </c>
+      <c r="I10">
+        <v>11.07454314861207</v>
+      </c>
+      <c r="J10">
+        <v>11.88430211766331</v>
+      </c>
+      <c r="K10">
+        <v>14.01557586314087</v>
+      </c>
+      <c r="L10">
+        <v>2.566140000710484</v>
+      </c>
+      <c r="M10">
+        <v>4.440523157903022</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>5.809145493335502</v>
+      </c>
+      <c r="C11">
+        <v>43.80568125499558</v>
+      </c>
+      <c r="D11">
+        <v>4.969085789616813</v>
+      </c>
+      <c r="E11">
+        <v>15.49297970566271</v>
+      </c>
+      <c r="F11">
+        <v>7.277224933710413</v>
+      </c>
+      <c r="G11">
+        <v>3.466245561618275</v>
+      </c>
+      <c r="H11">
+        <v>6.450411929348247</v>
+      </c>
+      <c r="I11">
+        <v>11.22789640693645</v>
+      </c>
+      <c r="J11">
+        <v>10.8597827585541</v>
+      </c>
+      <c r="K11">
+        <v>16.3980337296549</v>
+      </c>
+      <c r="L11">
+        <v>2.943132364067676</v>
+      </c>
+      <c r="M11">
+        <v>4.692653728505976</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>5.400772953307841</v>
+      </c>
+      <c r="C12">
+        <v>36.4818423562836</v>
+      </c>
+      <c r="D12">
+        <v>5.345867643625734</v>
+      </c>
+      <c r="E12">
+        <v>12.90947549484604</v>
+      </c>
+      <c r="F12">
+        <v>5.032238671287409</v>
+      </c>
+      <c r="G12">
+        <v>4.13664047589622</v>
+      </c>
+      <c r="H12">
+        <v>7.182244898859302</v>
+      </c>
+      <c r="I12">
+        <v>9.808784210780406</v>
+      </c>
+      <c r="J12">
+        <v>9.943011077377713</v>
+      </c>
+      <c r="K12">
+        <v>16.15137409602901</v>
+      </c>
+      <c r="L12">
+        <v>2.851578477446991</v>
+      </c>
+      <c r="M12">
+        <v>5.153219264045873</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5.718190489171315</v>
+      </c>
+      <c r="C13">
+        <v>65.93406161712177</v>
+      </c>
+      <c r="D13">
+        <v>5.289902090111934</v>
+      </c>
+      <c r="E13">
+        <v>16.26397327374924</v>
+      </c>
+      <c r="F13">
+        <v>5.449984596186688</v>
+      </c>
+      <c r="G13">
+        <v>3.373588135764631</v>
+      </c>
+      <c r="H13">
+        <v>6.352815424207417</v>
+      </c>
+      <c r="I13">
+        <v>9.768602399824678</v>
+      </c>
+      <c r="J13">
+        <v>12.09580261445819</v>
+      </c>
+      <c r="K13">
+        <v>13.77444072706668</v>
+      </c>
+      <c r="L13">
+        <v>3.171578745563035</v>
+      </c>
+      <c r="M13">
+        <v>4.641905963685974</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>5.844957280733381</v>
+      </c>
+      <c r="C14">
+        <v>33.98088148304015</v>
+      </c>
+      <c r="D14">
+        <v>4.784119523409654</v>
+      </c>
+      <c r="E14">
+        <v>14.23945280072857</v>
+      </c>
+      <c r="F14">
+        <v>4.863215881642399</v>
+      </c>
+      <c r="G14">
+        <v>2.731892140298864</v>
+      </c>
+      <c r="H14">
+        <v>5.840341338245266</v>
+      </c>
+      <c r="I14">
+        <v>10.03848469773556</v>
+      </c>
+      <c r="J14">
+        <v>11.50786873419352</v>
+      </c>
+      <c r="K14">
+        <v>13.88545510390364</v>
+      </c>
+      <c r="L14">
+        <v>2.523345525006838</v>
+      </c>
+      <c r="M14">
+        <v>4.399845424081461</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>3.011328764110506</v>
+      </c>
+      <c r="C15">
+        <v>21.23431533929238</v>
+      </c>
+      <c r="D15">
+        <v>2.697276655180699</v>
+      </c>
+      <c r="E15">
+        <v>8.952906207330152</v>
+      </c>
+      <c r="F15">
+        <v>2.583946037826591</v>
+      </c>
+      <c r="G15">
+        <v>1.420415814524338</v>
+      </c>
+      <c r="H15">
+        <v>3.200656758911228</v>
+      </c>
+      <c r="I15">
+        <v>5.416464075623624</v>
+      </c>
+      <c r="J15">
+        <v>5.151044745511222</v>
+      </c>
+      <c r="K15">
+        <v>7.655651203388474</v>
+      </c>
+      <c r="L15">
+        <v>1.397619386001971</v>
+      </c>
+      <c r="M15">
+        <v>2.248346096069193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4.912697407505108</v>
+      </c>
+      <c r="C2">
+        <v>24.26319721906234</v>
+      </c>
+      <c r="D2">
+        <v>4.324708906468424</v>
+      </c>
+      <c r="E2">
+        <v>13.10167594731925</v>
+      </c>
+      <c r="F2">
+        <v>4.578248455915082</v>
+      </c>
+      <c r="G2">
+        <v>3.295026471059417</v>
+      </c>
+      <c r="H2">
+        <v>5.038701133606147</v>
+      </c>
+      <c r="I2">
+        <v>9.522314864741229</v>
+      </c>
+      <c r="J2">
+        <v>9.928348139260574</v>
+      </c>
+      <c r="K2">
+        <v>14.99863910483803</v>
+      </c>
+      <c r="L2">
+        <v>2.693030461323722</v>
+      </c>
+      <c r="M2">
+        <v>4.605103800641801</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>5.014483328778505</v>
+      </c>
+      <c r="C3">
+        <v>26.16417452788204</v>
+      </c>
+      <c r="D3">
+        <v>4.002567902248015</v>
+      </c>
+      <c r="E3">
+        <v>14.00338515513073</v>
+      </c>
+      <c r="F3">
+        <v>4.629792420371222</v>
+      </c>
+      <c r="G3">
+        <v>2.950679797993036</v>
+      </c>
+      <c r="H3">
+        <v>5.334776519471077</v>
+      </c>
+      <c r="I3">
+        <v>11.31081233467067</v>
+      </c>
+      <c r="J3">
+        <v>10.3917662704189</v>
+      </c>
+      <c r="K3">
+        <v>13.29439382398369</v>
+      </c>
+      <c r="L3">
+        <v>2.300810117863243</v>
+      </c>
+      <c r="M3">
+        <v>4.389893074446481</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>4.470786974789741</v>
+      </c>
+      <c r="C4">
+        <v>28.98870103292893</v>
+      </c>
+      <c r="D4">
+        <v>4.678636783969589</v>
+      </c>
+      <c r="E4">
+        <v>12.37498889944348</v>
+      </c>
+      <c r="F4">
+        <v>4.891395253392661</v>
+      </c>
+      <c r="G4">
+        <v>2.976815242842345</v>
+      </c>
+      <c r="H4">
+        <v>5.265013684293117</v>
+      </c>
+      <c r="I4">
+        <v>9.263730531179588</v>
+      </c>
+      <c r="J4">
+        <v>11.73450010305552</v>
+      </c>
+      <c r="K4">
+        <v>15.90544844966313</v>
+      </c>
+      <c r="L4">
+        <v>2.333643161215545</v>
+      </c>
+      <c r="M4">
+        <v>4.072653547930511</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4.838425839969454</v>
+      </c>
+      <c r="C5">
+        <v>26.48456461634016</v>
+      </c>
+      <c r="D5">
+        <v>3.802932611615216</v>
+      </c>
+      <c r="E5">
+        <v>12.12500102001515</v>
+      </c>
+      <c r="F5">
+        <v>4.994995154654816</v>
+      </c>
+      <c r="G5">
+        <v>3.410754002601589</v>
+      </c>
+      <c r="H5">
+        <v>5.9331028743417</v>
+      </c>
+      <c r="I5">
+        <v>11.96396060848642</v>
+      </c>
+      <c r="J5">
+        <v>9.670762267779347</v>
+      </c>
+      <c r="K5">
+        <v>18.49196791463107</v>
+      </c>
+      <c r="L5">
+        <v>2.296958030357034</v>
+      </c>
+      <c r="M5">
+        <v>4.649206943150784</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>6.127724198539114</v>
+      </c>
+      <c r="C6">
+        <v>35.733395846622</v>
+      </c>
+      <c r="D6">
+        <v>3.676045052131931</v>
+      </c>
+      <c r="E6">
+        <v>15.4063203573333</v>
+      </c>
+      <c r="F6">
+        <v>4.834657960541141</v>
+      </c>
+      <c r="G6">
+        <v>3.286616611791349</v>
+      </c>
+      <c r="H6">
+        <v>5.805546688534231</v>
+      </c>
+      <c r="I6">
+        <v>11.41721538705517</v>
+      </c>
+      <c r="J6">
+        <v>9.365975305753109</v>
+      </c>
+      <c r="K6">
+        <v>14.60562559580327</v>
+      </c>
+      <c r="L6">
+        <v>2.685000823370979</v>
+      </c>
+      <c r="M6">
+        <v>4.543585077500088</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5.109671004636389</v>
+      </c>
+      <c r="C7">
+        <v>33.84064069572609</v>
+      </c>
+      <c r="D7">
+        <v>3.991906428720948</v>
+      </c>
+      <c r="E7">
+        <v>12.94071077033836</v>
+      </c>
+      <c r="F7">
+        <v>4.742444784461457</v>
+      </c>
+      <c r="G7">
+        <v>3.131622319326757</v>
+      </c>
+      <c r="H7">
+        <v>5.601988444042229</v>
+      </c>
+      <c r="I7">
+        <v>11.08277852050189</v>
+      </c>
+      <c r="J7">
+        <v>9.710836377306359</v>
+      </c>
+      <c r="K7">
+        <v>14.12512546779744</v>
+      </c>
+      <c r="L7">
+        <v>2.570691158554664</v>
+      </c>
+      <c r="M7">
+        <v>4.247708691501042</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5.497627019202823</v>
+      </c>
+      <c r="C8">
+        <v>37.9825752239272</v>
+      </c>
+      <c r="D8">
+        <v>4.649959312652776</v>
+      </c>
+      <c r="E8">
+        <v>16.43316690585362</v>
+      </c>
+      <c r="F8">
+        <v>5.013322003368592</v>
+      </c>
+      <c r="G8">
+        <v>3.683310428745417</v>
+      </c>
+      <c r="H8">
+        <v>6.161074058205409</v>
+      </c>
+      <c r="I8">
+        <v>12.50089467450232</v>
+      </c>
+      <c r="J8">
+        <v>11.53556713786412</v>
+      </c>
+      <c r="K8">
+        <v>15.66915297181068</v>
+      </c>
+      <c r="L8">
+        <v>2.67647079672481</v>
+      </c>
+      <c r="M8">
+        <v>4.099500745785307</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5.473630646850649</v>
+      </c>
+      <c r="C9">
+        <v>35.38185975543489</v>
+      </c>
+      <c r="D9">
+        <v>4.740562057293507</v>
+      </c>
+      <c r="E9">
+        <v>15.33166491607292</v>
+      </c>
+      <c r="F9">
+        <v>5.026134120829043</v>
+      </c>
+      <c r="G9">
+        <v>2.724702668796694</v>
+      </c>
+      <c r="H9">
+        <v>5.172536716924252</v>
+      </c>
+      <c r="I9">
+        <v>13.84701907999673</v>
+      </c>
+      <c r="J9">
+        <v>12.11873855924429</v>
+      </c>
+      <c r="K9">
+        <v>13.16631858490031</v>
+      </c>
+      <c r="L9">
+        <v>2.583005870796699</v>
+      </c>
+      <c r="M9">
+        <v>4.147742048234455</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>5.641144705854895</v>
+      </c>
+      <c r="C10">
+        <v>34.83524320236246</v>
+      </c>
+      <c r="D10">
+        <v>5.200067982106605</v>
+      </c>
+      <c r="E10">
+        <v>16.29218935927738</v>
+      </c>
+      <c r="F10">
+        <v>5.985658367415643</v>
+      </c>
+      <c r="G10">
+        <v>3.980013967455729</v>
+      </c>
+      <c r="H10">
+        <v>5.564384391020205</v>
+      </c>
+      <c r="I10">
+        <v>11.69508328536228</v>
+      </c>
+      <c r="J10">
+        <v>12.55284254328138</v>
+      </c>
+      <c r="K10">
+        <v>14.61299672977785</v>
+      </c>
+      <c r="L10">
+        <v>2.929827505064051</v>
+      </c>
+      <c r="M10">
+        <v>4.688353663582729</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>5.648607258153838</v>
+      </c>
+      <c r="C11">
+        <v>46.71358432681334</v>
+      </c>
+      <c r="D11">
+        <v>4.928767609922772</v>
+      </c>
+      <c r="E11">
+        <v>15.65703492833205</v>
+      </c>
+      <c r="F11">
+        <v>6.529238304965761</v>
+      </c>
+      <c r="G11">
+        <v>3.569319855262529</v>
+      </c>
+      <c r="H11">
+        <v>6.502361439390461</v>
+      </c>
+      <c r="I11">
+        <v>11.3030624773367</v>
+      </c>
+      <c r="J11">
+        <v>10.7031428721199</v>
+      </c>
+      <c r="K11">
+        <v>16.42905388632026</v>
+      </c>
+      <c r="L11">
+        <v>2.96242128932911</v>
+      </c>
+      <c r="M11">
+        <v>4.923114037997046</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>5.584098254169383</v>
+      </c>
+      <c r="C12">
+        <v>36.48974368933054</v>
+      </c>
+      <c r="D12">
+        <v>5.488141924755609</v>
+      </c>
+      <c r="E12">
+        <v>13.45021647012651</v>
+      </c>
+      <c r="F12">
+        <v>5.101462986777654</v>
+      </c>
+      <c r="G12">
+        <v>4.219002642104652</v>
+      </c>
+      <c r="H12">
+        <v>7.441023320204051</v>
+      </c>
+      <c r="I12">
+        <v>10.03896652086116</v>
+      </c>
+      <c r="J12">
+        <v>10.14347079410312</v>
+      </c>
+      <c r="K12">
+        <v>16.192072204311</v>
+      </c>
+      <c r="L12">
+        <v>2.928130514992404</v>
+      </c>
+      <c r="M12">
+        <v>5.394844538618257</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5.776686894205137</v>
+      </c>
+      <c r="C13">
+        <v>75.25048096028368</v>
+      </c>
+      <c r="D13">
+        <v>5.232046297117255</v>
+      </c>
+      <c r="E13">
+        <v>16.71278699113314</v>
+      </c>
+      <c r="F13">
+        <v>5.634263718390546</v>
+      </c>
+      <c r="G13">
+        <v>3.523437546753659</v>
+      </c>
+      <c r="H13">
+        <v>6.644645930307025</v>
+      </c>
+      <c r="I13">
+        <v>9.978209334544404</v>
+      </c>
+      <c r="J13">
+        <v>12.46042443954272</v>
+      </c>
+      <c r="K13">
+        <v>14.02069282426549</v>
+      </c>
+      <c r="L13">
+        <v>3.217360206339153</v>
+      </c>
+      <c r="M13">
+        <v>4.906674989529294</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>5.97451466498412</v>
+      </c>
+      <c r="C14">
+        <v>33.98088148304015</v>
+      </c>
+      <c r="D14">
+        <v>5.035548641296628</v>
+      </c>
+      <c r="E14">
+        <v>14.28856444721522</v>
+      </c>
+      <c r="F14">
+        <v>5.193453806876534</v>
+      </c>
+      <c r="G14">
+        <v>2.818735813056652</v>
+      </c>
+      <c r="H14">
+        <v>5.83247009819761</v>
+      </c>
+      <c r="I14">
+        <v>10.21303857353818</v>
+      </c>
+      <c r="J14">
+        <v>11.90502995804908</v>
+      </c>
+      <c r="K14">
+        <v>13.85482177154212</v>
+      </c>
+      <c r="L14">
+        <v>2.49604198472233</v>
+      </c>
+      <c r="M14">
+        <v>4.687344070489656</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>3.109225077734864</v>
+      </c>
+      <c r="C15">
+        <v>21.51441389611958</v>
+      </c>
+      <c r="D15">
+        <v>2.685143945723477</v>
+      </c>
+      <c r="E15">
+        <v>9.026830989559883</v>
+      </c>
+      <c r="F15">
+        <v>2.699804897804296</v>
+      </c>
+      <c r="G15">
+        <v>1.466669716959992</v>
+      </c>
+      <c r="H15">
+        <v>3.234752121250274</v>
+      </c>
+      <c r="I15">
+        <v>5.525055130635562</v>
+      </c>
+      <c r="J15">
+        <v>5.309366948768028</v>
+      </c>
+      <c r="K15">
+        <v>7.798114314328378</v>
+      </c>
+      <c r="L15">
+        <v>1.434165225397692</v>
+      </c>
+      <c r="M15">
+        <v>2.323109702251587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>10.88403956732931</v>
+      </c>
+      <c r="C2">
+        <v>97.95862972687051</v>
+      </c>
+      <c r="D2">
+        <v>20.48291298163564</v>
+      </c>
+      <c r="E2">
+        <v>65.68328847628828</v>
+      </c>
+      <c r="F2">
+        <v>25.47990644701036</v>
+      </c>
+      <c r="G2">
+        <v>14.76037873131403</v>
+      </c>
+      <c r="H2">
+        <v>27.33570893985508</v>
+      </c>
+      <c r="I2">
+        <v>34.45995225220212</v>
+      </c>
+      <c r="J2">
+        <v>68.96494160734969</v>
+      </c>
+      <c r="K2">
+        <v>77.89564059170181</v>
+      </c>
+      <c r="L2">
+        <v>8.266579299781277</v>
+      </c>
+      <c r="M2">
+        <v>13.78181371635161</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>11.6724209837856</v>
+      </c>
+      <c r="C3">
+        <v>72.4795144168605</v>
+      </c>
+      <c r="D3">
+        <v>19.63704327708712</v>
+      </c>
+      <c r="F3">
+        <v>24.77687208223063</v>
+      </c>
+      <c r="G3">
+        <v>16.03491450719439</v>
+      </c>
+      <c r="H3">
+        <v>25.08431355666757</v>
+      </c>
+      <c r="I3">
+        <v>36.71374630752774</v>
+      </c>
+      <c r="J3">
+        <v>43.74813813823339</v>
+      </c>
+      <c r="K3">
+        <v>54.97424697707088</v>
+      </c>
+      <c r="L3">
+        <v>7.633871457194735</v>
+      </c>
+      <c r="M3">
+        <v>12.42194230886655</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>11.34391467638396</v>
+      </c>
+      <c r="C4">
+        <v>75.95697172487689</v>
+      </c>
+      <c r="D4">
+        <v>21.41399425332351</v>
+      </c>
+      <c r="F4">
+        <v>21.52273184534238</v>
+      </c>
+      <c r="G4">
+        <v>13.42694766356914</v>
+      </c>
+      <c r="H4">
+        <v>27.64530225922303</v>
+      </c>
+      <c r="I4">
+        <v>36.99147368692236</v>
+      </c>
+      <c r="J4">
+        <v>61.33549998290628</v>
+      </c>
+      <c r="K4">
+        <v>52.89539115584287</v>
+      </c>
+      <c r="L4">
+        <v>7.586709727342071</v>
+      </c>
+      <c r="M4">
+        <v>11.34331007063474</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>11.3747842226693</v>
+      </c>
+      <c r="D5">
+        <v>19.34989699386448</v>
+      </c>
+      <c r="F5">
+        <v>24.94692922135104</v>
+      </c>
+      <c r="G5">
+        <v>14.36963169826618</v>
+      </c>
+      <c r="H5">
+        <v>28.27597948751253</v>
+      </c>
+      <c r="I5">
+        <v>59.70136706181925</v>
+      </c>
+      <c r="J5">
+        <v>75.25396990267464</v>
+      </c>
+      <c r="K5">
+        <v>73.63994600847651</v>
+      </c>
+      <c r="L5">
+        <v>9.649432885151224</v>
+      </c>
+      <c r="M5">
+        <v>11.57271628771674</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>11.62816377011928</v>
+      </c>
+      <c r="D6">
+        <v>21.46974308926088</v>
+      </c>
+      <c r="E6">
+        <v>100.1133102715493</v>
+      </c>
+      <c r="F6">
+        <v>41.21891151220803</v>
+      </c>
+      <c r="G6">
+        <v>18.57419183046546</v>
+      </c>
+      <c r="H6">
+        <v>24.06790391691728</v>
+      </c>
+      <c r="I6">
+        <v>49.75759320722805</v>
+      </c>
+      <c r="J6">
+        <v>106.692428108727</v>
+      </c>
+      <c r="K6">
+        <v>83.41589813453382</v>
+      </c>
+      <c r="L6">
+        <v>10.35046128337364</v>
+      </c>
+      <c r="M6">
+        <v>13.87824165591148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>12.95947060585731</v>
+      </c>
+      <c r="D7">
+        <v>27.76181202134293</v>
+      </c>
+      <c r="F7">
+        <v>25.27502292619443</v>
+      </c>
+      <c r="G7">
+        <v>13.66761652723121</v>
+      </c>
+      <c r="H7">
+        <v>22.73429228823811</v>
+      </c>
+      <c r="I7">
+        <v>52.74349959517398</v>
+      </c>
+      <c r="J7">
+        <v>59.31532213932626</v>
+      </c>
+      <c r="K7">
+        <v>48.10069610773503</v>
+      </c>
+      <c r="L7">
+        <v>8.547235735092922</v>
+      </c>
+      <c r="M7">
+        <v>13.82472557181569</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>13.18107422646523</v>
+      </c>
+      <c r="D8">
+        <v>22.28752220455651</v>
+      </c>
+      <c r="E8">
+        <v>99.85496843081762</v>
+      </c>
+      <c r="F8">
+        <v>24.52399659771746</v>
+      </c>
+      <c r="G8">
+        <v>16.19789188166041</v>
+      </c>
+      <c r="H8">
+        <v>21.06455160606996</v>
+      </c>
+      <c r="I8">
+        <v>43.54310974008829</v>
+      </c>
+      <c r="J8">
+        <v>74.59438748259728</v>
+      </c>
+      <c r="K8">
+        <v>83.03927580549446</v>
+      </c>
+      <c r="L8">
+        <v>8.913550436737824</v>
+      </c>
+      <c r="M8">
+        <v>13.04747503635194</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>14.2486398225663</v>
+      </c>
+      <c r="C9">
+        <v>104.7498637518742</v>
+      </c>
+      <c r="D9">
+        <v>23.0869722334393</v>
+      </c>
+      <c r="F9">
+        <v>30.57481579683628</v>
+      </c>
+      <c r="G9">
+        <v>16.05515178672657</v>
+      </c>
+      <c r="H9">
+        <v>29.10047426970458</v>
+      </c>
+      <c r="I9">
+        <v>64.04001361320229</v>
+      </c>
+      <c r="J9">
+        <v>48.72200412305921</v>
+      </c>
+      <c r="K9">
+        <v>61.64399213813948</v>
+      </c>
+      <c r="L9">
+        <v>8.322393034767737</v>
+      </c>
+      <c r="M9">
+        <v>13.79733115023973</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>16.63314632266364</v>
+      </c>
+      <c r="D10">
+        <v>29.0669930763188</v>
+      </c>
+      <c r="F10">
+        <v>55.08833475185389</v>
+      </c>
+      <c r="G10">
+        <v>25.18092250136463</v>
+      </c>
+      <c r="H10">
+        <v>50.27050000914804</v>
+      </c>
+      <c r="I10">
+        <v>53.76739997211524</v>
+      </c>
+      <c r="J10">
+        <v>109.3373875642813</v>
+      </c>
+      <c r="K10">
+        <v>105.8182301671925</v>
+      </c>
+      <c r="L10">
+        <v>10.38945690122544</v>
+      </c>
+      <c r="M10">
+        <v>14.39507992235084</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>19.23032978552235</v>
+      </c>
+      <c r="C11">
+        <v>106.3607346536877</v>
+      </c>
+      <c r="D11">
+        <v>28.46718368645864</v>
+      </c>
+      <c r="F11">
+        <v>43.04452963359602</v>
+      </c>
+      <c r="G11">
+        <v>27.72774884392102</v>
+      </c>
+      <c r="H11">
+        <v>38.57558909172776</v>
+      </c>
+      <c r="I11">
+        <v>60.15276779950683</v>
+      </c>
+      <c r="J11">
+        <v>93.7459183343129</v>
+      </c>
+      <c r="K11">
+        <v>74.9661352227926</v>
+      </c>
+      <c r="L11">
+        <v>14.30863576736613</v>
+      </c>
+      <c r="M11">
+        <v>18.89715525346656</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>23.00765219995634</v>
+      </c>
+      <c r="C12">
+        <v>104.2658975484439</v>
+      </c>
+      <c r="D12">
+        <v>32.11655720962137</v>
+      </c>
+      <c r="F12">
+        <v>48.65564042170303</v>
+      </c>
+      <c r="G12">
+        <v>18.69969766841804</v>
+      </c>
+      <c r="H12">
+        <v>37.06520248493438</v>
+      </c>
+      <c r="I12">
+        <v>38.55987763448275</v>
+      </c>
+      <c r="J12">
+        <v>51.19653117965146</v>
+      </c>
+      <c r="K12">
+        <v>48.36449293923646</v>
+      </c>
+      <c r="L12">
+        <v>9.79262047423582</v>
+      </c>
+      <c r="M12">
+        <v>16.01610380572933</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>16.96573346064504</v>
+      </c>
+      <c r="D13">
+        <v>25.19079835699459</v>
+      </c>
+      <c r="E13">
+        <v>74.69885068585307</v>
+      </c>
+      <c r="F13">
+        <v>29.97041284958615</v>
+      </c>
+      <c r="G13">
+        <v>17.48662802167587</v>
+      </c>
+      <c r="H13">
+        <v>25.24071411037167</v>
+      </c>
+      <c r="I13">
+        <v>45.30822072482657</v>
+      </c>
+      <c r="J13">
+        <v>39.92486207426452</v>
+      </c>
+      <c r="K13">
+        <v>93.51873053818154</v>
+      </c>
+      <c r="L13">
+        <v>9.858174161410171</v>
+      </c>
+      <c r="M13">
+        <v>26.26350893437704</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>16.00738646197612</v>
+      </c>
+      <c r="D14">
+        <v>22.91298956339881</v>
+      </c>
+      <c r="E14">
+        <v>70.34402702576243</v>
+      </c>
+      <c r="F14">
+        <v>30.88895958590369</v>
+      </c>
+      <c r="G14">
+        <v>18.66247798767978</v>
+      </c>
+      <c r="H14">
+        <v>22.16634046368916</v>
+      </c>
+      <c r="I14">
+        <v>41.41763978466046</v>
+      </c>
+      <c r="J14">
+        <v>49.43776467894947</v>
+      </c>
+      <c r="K14">
+        <v>47.20304766192323</v>
+      </c>
+      <c r="L14">
+        <v>9.135358801745452</v>
+      </c>
+      <c r="M14">
+        <v>15.49094013565183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>8.440816389719373</v>
+      </c>
+      <c r="D15">
+        <v>16.69240848621936</v>
+      </c>
+      <c r="F15">
+        <v>19.36705595780691</v>
+      </c>
+      <c r="G15">
+        <v>9.53087037809791</v>
+      </c>
+      <c r="H15">
+        <v>13.00723158608827</v>
+      </c>
+      <c r="I15">
+        <v>16.85336664081954</v>
+      </c>
+      <c r="J15">
+        <v>44.38849190150099</v>
+      </c>
+      <c r="K15">
+        <v>25.04653487984018</v>
+      </c>
+      <c r="L15">
+        <v>4.822720847207865</v>
+      </c>
+      <c r="M15">
+        <v>7.884149019229858</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13.06051970588445</v>
+      </c>
+      <c r="C2">
+        <v>97.95862972687053</v>
+      </c>
+      <c r="D2">
+        <v>25.00257056552407</v>
+      </c>
+      <c r="E2">
+        <v>66.05895387138429</v>
+      </c>
+      <c r="F2">
+        <v>35.64091798002088</v>
+      </c>
+      <c r="G2">
+        <v>20.59143742420957</v>
+      </c>
+      <c r="H2">
+        <v>32.24918674553307</v>
+      </c>
+      <c r="I2">
+        <v>49.09199329211687</v>
+      </c>
+      <c r="J2">
+        <v>71.54848095867294</v>
+      </c>
+      <c r="K2">
+        <v>77.03201414857267</v>
+      </c>
+      <c r="L2">
+        <v>9.463035311910666</v>
+      </c>
+      <c r="M2">
+        <v>13.96895799631572</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>13.37468161767797</v>
+      </c>
+      <c r="C3">
+        <v>68.9335915012973</v>
+      </c>
+      <c r="D3">
+        <v>21.32562679043168</v>
+      </c>
+      <c r="F3">
+        <v>33.68418159384515</v>
+      </c>
+      <c r="G3">
+        <v>17.78121104513171</v>
+      </c>
+      <c r="H3">
+        <v>29.06632009619359</v>
+      </c>
+      <c r="I3">
+        <v>41.87702928846286</v>
+      </c>
+      <c r="J3">
+        <v>49.12777645930105</v>
+      </c>
+      <c r="K3">
+        <v>53.99543054435556</v>
+      </c>
+      <c r="L3">
+        <v>9.212745108200798</v>
+      </c>
+      <c r="M3">
+        <v>13.02079510607365</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>13.14515343095321</v>
+      </c>
+      <c r="C4">
+        <v>82.745847062506</v>
+      </c>
+      <c r="D4">
+        <v>25.79257114956959</v>
+      </c>
+      <c r="F4">
+        <v>24.86923989826635</v>
+      </c>
+      <c r="G4">
+        <v>17.28486777385459</v>
+      </c>
+      <c r="H4">
+        <v>30.00876813908369</v>
+      </c>
+      <c r="I4">
+        <v>52.28030652607627</v>
+      </c>
+      <c r="J4">
+        <v>61.22180927521831</v>
+      </c>
+      <c r="K4">
+        <v>52.38372423042475</v>
+      </c>
+      <c r="L4">
+        <v>8.83832827370429</v>
+      </c>
+      <c r="M4">
+        <v>12.04928587504501</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>12.2745773291146</v>
+      </c>
+      <c r="D5">
+        <v>21.46661892468845</v>
+      </c>
+      <c r="F5">
+        <v>27.06045415055887</v>
+      </c>
+      <c r="G5">
+        <v>16.14617953333519</v>
+      </c>
+      <c r="H5">
+        <v>32.59580203318911</v>
+      </c>
+      <c r="I5">
+        <v>69.34911796257366</v>
+      </c>
+      <c r="J5">
+        <v>78.23643978954827</v>
+      </c>
+      <c r="K5">
+        <v>75.92367603949015</v>
+      </c>
+      <c r="L5">
+        <v>10.11219064354203</v>
+      </c>
+      <c r="M5">
+        <v>11.38515437738278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>12.74656310213323</v>
+      </c>
+      <c r="D6">
+        <v>23.02492222770072</v>
+      </c>
+      <c r="E6">
+        <v>100.1133102715493</v>
+      </c>
+      <c r="F6">
+        <v>41.91171039075667</v>
+      </c>
+      <c r="G6">
+        <v>21.98183721864885</v>
+      </c>
+      <c r="H6">
+        <v>25.82523050447608</v>
+      </c>
+      <c r="I6">
+        <v>48.89747612034444</v>
+      </c>
+      <c r="J6">
+        <v>106.692428108727</v>
+      </c>
+      <c r="K6">
+        <v>87.0297639872767</v>
+      </c>
+      <c r="L6">
+        <v>11.98875771414853</v>
+      </c>
+      <c r="M6">
+        <v>14.13466916119175</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>14.81770870041462</v>
+      </c>
+      <c r="D7">
+        <v>30.54495004728628</v>
+      </c>
+      <c r="F7">
+        <v>31.56860274874189</v>
+      </c>
+      <c r="G7">
+        <v>16.41977054771604</v>
+      </c>
+      <c r="H7">
+        <v>26.54741790706277</v>
+      </c>
+      <c r="I7">
+        <v>51.47577828481194</v>
+      </c>
+      <c r="J7">
+        <v>62.15024840332354</v>
+      </c>
+      <c r="K7">
+        <v>57.97228105723156</v>
+      </c>
+      <c r="L7">
+        <v>8.761283788599993</v>
+      </c>
+      <c r="M7">
+        <v>15.3907518723124</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>13.53898433370722</v>
+      </c>
+      <c r="D8">
+        <v>25.06408399696877</v>
+      </c>
+      <c r="E8">
+        <v>99.85496843081762</v>
+      </c>
+      <c r="F8">
+        <v>25.22819328482898</v>
+      </c>
+      <c r="G8">
+        <v>20.13340423463137</v>
+      </c>
+      <c r="H8">
+        <v>22.43710391110071</v>
+      </c>
+      <c r="I8">
+        <v>49.54007534864434</v>
+      </c>
+      <c r="J8">
+        <v>84.97712547020704</v>
+      </c>
+      <c r="K8">
+        <v>89.613101948579</v>
+      </c>
+      <c r="L8">
+        <v>10.29943318945102</v>
+      </c>
+      <c r="M8">
+        <v>12.94608428859329</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>15.50812454604493</v>
+      </c>
+      <c r="C9">
+        <v>104.7498637518742</v>
+      </c>
+      <c r="D9">
+        <v>28.03223635036953</v>
+      </c>
+      <c r="F9">
+        <v>35.90187368255865</v>
+      </c>
+      <c r="G9">
+        <v>22.05341313647074</v>
+      </c>
+      <c r="H9">
+        <v>33.90330672705551</v>
+      </c>
+      <c r="I9">
+        <v>66.2861768793632</v>
+      </c>
+      <c r="J9">
+        <v>49.98857317123316</v>
+      </c>
+      <c r="K9">
+        <v>61.05350137975564</v>
+      </c>
+      <c r="L9">
+        <v>9.171288024654075</v>
+      </c>
+      <c r="M9">
+        <v>14.47667379156451</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>18.31411642524297</v>
+      </c>
+      <c r="D10">
+        <v>32.04783984037337</v>
+      </c>
+      <c r="F10">
+        <v>56.52264821518372</v>
+      </c>
+      <c r="G10">
+        <v>24.9585696410692</v>
+      </c>
+      <c r="H10">
+        <v>47.71431862830468</v>
+      </c>
+      <c r="I10">
+        <v>59.42989459401725</v>
+      </c>
+      <c r="J10">
+        <v>109.3373875642813</v>
+      </c>
+      <c r="K10">
+        <v>105.8182301671926</v>
+      </c>
+      <c r="L10">
+        <v>11.88932176602197</v>
+      </c>
+      <c r="M10">
+        <v>14.55610469781471</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>18.71038870160313</v>
+      </c>
+      <c r="C11">
+        <v>106.3607346536877</v>
+      </c>
+      <c r="D11">
+        <v>31.08408675778152</v>
+      </c>
+      <c r="F11">
+        <v>45.22232126995625</v>
+      </c>
+      <c r="G11">
+        <v>44.47102247075268</v>
+      </c>
+      <c r="H11">
+        <v>37.49891868290691</v>
+      </c>
+      <c r="I11">
+        <v>66.11517146988412</v>
+      </c>
+      <c r="J11">
+        <v>93.7459183343129</v>
+      </c>
+      <c r="K11">
+        <v>86.70577884642732</v>
+      </c>
+      <c r="L11">
+        <v>15.64621366980357</v>
+      </c>
+      <c r="M11">
+        <v>18.77344420130546</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>20.23048273003948</v>
+      </c>
+      <c r="C12">
+        <v>104.2658975484439</v>
+      </c>
+      <c r="D12">
+        <v>34.29137684446297</v>
+      </c>
+      <c r="F12">
+        <v>46.90843502269945</v>
+      </c>
+      <c r="G12">
+        <v>24.23651756014295</v>
+      </c>
+      <c r="H12">
+        <v>40.85751408390479</v>
+      </c>
+      <c r="I12">
+        <v>42.31890966376575</v>
+      </c>
+      <c r="J12">
+        <v>58.93130561258408</v>
+      </c>
+      <c r="K12">
+        <v>48.78844178841195</v>
+      </c>
+      <c r="L12">
+        <v>12.2163648626533</v>
+      </c>
+      <c r="M12">
+        <v>16.76013090781447</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>17.6542153685519</v>
+      </c>
+      <c r="D13">
+        <v>26.25250325439025</v>
+      </c>
+      <c r="E13">
+        <v>82.44927181896281</v>
+      </c>
+      <c r="F13">
+        <v>31.89286702374839</v>
+      </c>
+      <c r="G13">
+        <v>19.59193698768939</v>
+      </c>
+      <c r="H13">
+        <v>27.76884603547233</v>
+      </c>
+      <c r="I13">
+        <v>52.01937279490553</v>
+      </c>
+      <c r="J13">
+        <v>46.71102848187128</v>
+      </c>
+      <c r="K13">
+        <v>93.51873053818156</v>
+      </c>
+      <c r="L13">
+        <v>10.99422156897608</v>
+      </c>
+      <c r="M13">
+        <v>26.32878128729407</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>19.22271996217058</v>
+      </c>
+      <c r="D14">
+        <v>21.86771518390527</v>
+      </c>
+      <c r="E14">
+        <v>70.34402702576244</v>
+      </c>
+      <c r="F14">
+        <v>39.28430716403046</v>
+      </c>
+      <c r="G14">
+        <v>21.16133103132719</v>
+      </c>
+      <c r="H14">
+        <v>21.66179640470497</v>
+      </c>
+      <c r="I14">
+        <v>43.04628211236439</v>
+      </c>
+      <c r="J14">
+        <v>79.98212423910587</v>
+      </c>
+      <c r="K14">
+        <v>50.78443051047075</v>
+      </c>
+      <c r="L14">
+        <v>10.91855095760117</v>
+      </c>
+      <c r="M14">
+        <v>18.4440931058484</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>9.69149621992819</v>
+      </c>
+      <c r="D15">
+        <v>18.37969917316634</v>
+      </c>
+      <c r="F15">
+        <v>20.76907996618045</v>
+      </c>
+      <c r="G15">
+        <v>11.35897230358814</v>
+      </c>
+      <c r="H15">
+        <v>13.6970897488896</v>
+      </c>
+      <c r="I15">
+        <v>18.20209026058754</v>
+      </c>
+      <c r="J15">
+        <v>65.74269057249249</v>
+      </c>
+      <c r="K15">
+        <v>22.98513217862763</v>
+      </c>
+      <c r="L15">
+        <v>5.819586513418102</v>
+      </c>
+      <c r="M15">
+        <v>8.832909239354489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
         <v>13.82578216132719</v>
       </c>
       <c r="C2">
@@ -4313,40 +8240,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.259314026947806</v>
+        <v>720240.53665396</v>
       </c>
       <c r="C2">
-        <v>24.77470931554573</v>
+        <v>13108.75128929</v>
       </c>
       <c r="D2">
-        <v>4.233987073791424</v>
+        <v>937809.09265927</v>
       </c>
       <c r="E2">
-        <v>13.00466104342871</v>
+        <v>48909.6396915</v>
       </c>
       <c r="F2">
-        <v>4.581394321289869</v>
+        <v>396068.63978413</v>
       </c>
       <c r="G2">
-        <v>2.953079986300894</v>
+        <v>945599.45517607</v>
       </c>
       <c r="H2">
-        <v>4.671119521597542</v>
+        <v>283863.98425436</v>
       </c>
       <c r="I2">
-        <v>9.217611801967001</v>
+        <v>69958.74866442</v>
       </c>
       <c r="J2">
-        <v>9.331425489773185</v>
+        <v>80062.95907437</v>
       </c>
       <c r="K2">
-        <v>13.89229222252481</v>
+        <v>48410.71767877</v>
       </c>
       <c r="L2">
-        <v>2.471244029523893</v>
+        <v>1343096.37495249</v>
       </c>
       <c r="M2">
-        <v>4.121800638579302</v>
+        <v>533493.11782156</v>
       </c>
     </row>
     <row r="3">
@@ -4356,40 +8283,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>4.759075829736644</v>
+        <v>703405.2707537099</v>
       </c>
       <c r="C3">
-        <v>26.06594324618619</v>
+        <v>13490.499674</v>
       </c>
       <c r="D3">
-        <v>3.804791787181957</v>
+        <v>923091.42140407</v>
       </c>
       <c r="E3">
-        <v>12.52622823104816</v>
+        <v>41243.40564128</v>
       </c>
       <c r="F3">
-        <v>4.150578462442391</v>
+        <v>411017.59715102</v>
       </c>
       <c r="G3">
-        <v>2.896456042208567</v>
+        <v>1096099.09459146</v>
       </c>
       <c r="H3">
-        <v>5.013962143736643</v>
+        <v>280916.00807724</v>
       </c>
       <c r="I3">
-        <v>10.85672283777362</v>
+        <v>61709.81252199</v>
       </c>
       <c r="J3">
-        <v>9.476012462596222</v>
+        <v>86768.36198882</v>
       </c>
       <c r="K3">
-        <v>12.69626750469292</v>
+        <v>47964.81842372</v>
       </c>
       <c r="L3">
-        <v>2.201877131160674</v>
+        <v>1403770.0760129</v>
       </c>
       <c r="M3">
-        <v>4.167940872353753</v>
+        <v>559131.86157882</v>
       </c>
     </row>
     <row r="4">
@@ -4399,40 +8326,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>3.90155814828158</v>
+        <v>657064.13530722</v>
       </c>
       <c r="C4">
-        <v>29.18032049398214</v>
+        <v>11671.36968002</v>
       </c>
       <c r="D4">
-        <v>4.23978296948431</v>
+        <v>916057.16002658</v>
       </c>
       <c r="E4">
-        <v>12.51123935952304</v>
+        <v>38182.08593634</v>
       </c>
       <c r="F4">
-        <v>4.679322271809349</v>
+        <v>403260.55594598</v>
       </c>
       <c r="G4">
-        <v>2.81247070045096</v>
+        <v>1005789.73394198</v>
       </c>
       <c r="H4">
-        <v>4.966215972095638</v>
+        <v>251205.43575108</v>
       </c>
       <c r="I4">
-        <v>9.301496960665185</v>
+        <v>71262.89565532999</v>
       </c>
       <c r="J4">
-        <v>11.27801205222521</v>
+        <v>74412.17224807</v>
       </c>
       <c r="K4">
-        <v>15.30473086234856</v>
+        <v>26802.72761201</v>
       </c>
       <c r="L4">
-        <v>2.121379036943623</v>
+        <v>1515125.35969601</v>
       </c>
       <c r="M4">
-        <v>3.962916853970821</v>
+        <v>566654.84483172</v>
       </c>
     </row>
     <row r="5">
@@ -4442,40 +8369,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>4.387626588180623</v>
+        <v>647753.44778663</v>
       </c>
       <c r="C5">
-        <v>26.70011505543284</v>
+        <v>18805.55497685</v>
       </c>
       <c r="D5">
-        <v>3.676040446678344</v>
+        <v>901265.86601874</v>
       </c>
       <c r="E5">
-        <v>11.19876597441593</v>
+        <v>57482.45713074</v>
       </c>
       <c r="F5">
-        <v>4.790987906238347</v>
+        <v>378010.6498415</v>
       </c>
       <c r="G5">
-        <v>3.041386590180601</v>
+        <v>1032922.57112567</v>
       </c>
       <c r="H5">
-        <v>5.629516204470749</v>
+        <v>250510.84314955</v>
       </c>
       <c r="I5">
-        <v>11.1539533800914</v>
+        <v>74991.49715318</v>
       </c>
       <c r="J5">
-        <v>9.705942095983612</v>
+        <v>88200.20551425</v>
       </c>
       <c r="K5">
-        <v>16.99644740997108</v>
+        <v>41884.53100246</v>
       </c>
       <c r="L5">
-        <v>2.038840897899551</v>
+        <v>1537936.96528152</v>
       </c>
       <c r="M5">
-        <v>4.347967509808808</v>
+        <v>588218.44781192</v>
       </c>
     </row>
     <row r="6">
@@ -4485,40 +8412,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>5.402289780333358</v>
+        <v>676479.12043588</v>
       </c>
       <c r="C6">
-        <v>34.50268205265301</v>
+        <v>10023.8613814</v>
       </c>
       <c r="D6">
-        <v>3.730003146176953</v>
+        <v>850206.9286018501</v>
       </c>
       <c r="E6">
-        <v>14.34179298117949</v>
+        <v>55773.68380225</v>
       </c>
       <c r="F6">
-        <v>4.701181243961572</v>
+        <v>407273.1596013</v>
       </c>
       <c r="G6">
-        <v>3.13456539616592</v>
+        <v>993295.69130312</v>
       </c>
       <c r="H6">
-        <v>5.629128655789447</v>
+        <v>264843.71882887</v>
       </c>
       <c r="I6">
-        <v>10.57997719040547</v>
+        <v>64362.03210998</v>
       </c>
       <c r="J6">
-        <v>8.936858289700391</v>
+        <v>92518.78070126</v>
       </c>
       <c r="K6">
-        <v>13.88176819551973</v>
+        <v>46353.37222514</v>
       </c>
       <c r="L6">
-        <v>2.448945496977677</v>
+        <v>1538880.15128513</v>
       </c>
       <c r="M6">
-        <v>4.147572196881462</v>
+        <v>573756.71650262</v>
       </c>
     </row>
     <row r="7">
@@ -4528,40 +8455,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.093865264787558</v>
+        <v>616298.78124078</v>
       </c>
       <c r="C7">
-        <v>33.84236474066733</v>
+        <v>12369.21987353</v>
       </c>
       <c r="D7">
-        <v>3.907918265021192</v>
+        <v>812925.20347455</v>
       </c>
       <c r="E7">
-        <v>12.61250180233113</v>
+        <v>59685.77912335</v>
       </c>
       <c r="F7">
-        <v>4.742511424159299</v>
+        <v>397657.48475468</v>
       </c>
       <c r="G7">
-        <v>2.859763738786211</v>
+        <v>1017940.14039692</v>
       </c>
       <c r="H7">
-        <v>5.402766004342859</v>
+        <v>290170.11174415</v>
       </c>
       <c r="I7">
-        <v>11.14743336512764</v>
+        <v>64066.43337418</v>
       </c>
       <c r="J7">
-        <v>8.950081543412857</v>
+        <v>75187.20024716</v>
       </c>
       <c r="K7">
-        <v>12.7540877214365</v>
+        <v>42458.12763473</v>
       </c>
       <c r="L7">
-        <v>2.29842258155511</v>
+        <v>1536331.58671718</v>
       </c>
       <c r="M7">
-        <v>3.954120049889515</v>
+        <v>585778.07551746</v>
       </c>
     </row>
     <row r="8">
@@ -4571,40 +8498,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.083171597389869</v>
+        <v>618884.60516312</v>
       </c>
       <c r="C8">
-        <v>33.77149497886662</v>
+        <v>7306.87203876</v>
       </c>
       <c r="D8">
-        <v>4.61166714209377</v>
+        <v>804775.9506713999</v>
       </c>
       <c r="E8">
-        <v>15.65932139969655</v>
+        <v>48625.19270806</v>
       </c>
       <c r="F8">
-        <v>5.130895826102762</v>
+        <v>401422.23830174</v>
       </c>
       <c r="G8">
-        <v>3.593779973840045</v>
+        <v>981641.707131</v>
       </c>
       <c r="H8">
-        <v>5.921529570666448</v>
+        <v>281308.65987235</v>
       </c>
       <c r="I8">
-        <v>12.05346454577352</v>
+        <v>71928.38967153001</v>
       </c>
       <c r="J8">
-        <v>11.15023119929403</v>
+        <v>68948.05247383</v>
       </c>
       <c r="K8">
-        <v>13.61093766274534</v>
+        <v>44955.45719684</v>
       </c>
       <c r="L8">
-        <v>2.261189669037102</v>
+        <v>1573212.52371643</v>
       </c>
       <c r="M8">
-        <v>3.7801759261042</v>
+        <v>576584.61559266</v>
       </c>
     </row>
     <row r="9">
@@ -4614,40 +8541,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>5.081410872922184</v>
+        <v>600190.16303116</v>
       </c>
       <c r="C9">
-        <v>34.44190437999934</v>
+        <v>10939.60218407</v>
       </c>
       <c r="D9">
-        <v>4.859230799126681</v>
+        <v>872800.94212941</v>
       </c>
       <c r="E9">
-        <v>15.10003056022195</v>
+        <v>38837.31984075</v>
       </c>
       <c r="F9">
-        <v>4.993846388355517</v>
+        <v>391598.34471814</v>
       </c>
       <c r="G9">
-        <v>2.54655328156663</v>
+        <v>1047291.2240199</v>
       </c>
       <c r="H9">
-        <v>4.94993345903978</v>
+        <v>308537.94595496</v>
       </c>
       <c r="I9">
-        <v>13.37758168737181</v>
+        <v>94783.49275522</v>
       </c>
       <c r="J9">
-        <v>11.43894131402542</v>
+        <v>69753.48507859001</v>
       </c>
       <c r="K9">
-        <v>12.88453997086682</v>
+        <v>38877.2927275</v>
       </c>
       <c r="L9">
-        <v>2.213187648228128</v>
+        <v>1586136.42671119</v>
       </c>
       <c r="M9">
-        <v>3.774710422814934</v>
+        <v>611834.92471411</v>
       </c>
     </row>
     <row r="10">
@@ -4657,40 +8584,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>5.344193530294172</v>
+        <v>566154.0971495101</v>
       </c>
       <c r="C10">
-        <v>37.3440424891886</v>
+        <v>11680.74925581</v>
       </c>
       <c r="D10">
-        <v>4.645724093281102</v>
+        <v>787178.59873538</v>
       </c>
       <c r="E10">
-        <v>15.6519289050374</v>
+        <v>33958.84785321</v>
       </c>
       <c r="F10">
-        <v>5.612520754812202</v>
+        <v>331722.63551119</v>
       </c>
       <c r="G10">
-        <v>3.560342932784545</v>
+        <v>970798.691257</v>
       </c>
       <c r="H10">
-        <v>4.988390193044472</v>
+        <v>300315.526125</v>
       </c>
       <c r="I10">
-        <v>10.97565750278677</v>
+        <v>83605.99589987</v>
       </c>
       <c r="J10">
-        <v>11.46928253163459</v>
+        <v>67267.36222988</v>
       </c>
       <c r="K10">
-        <v>13.66982034775643</v>
+        <v>34552.08633412</v>
       </c>
       <c r="L10">
-        <v>2.45759010942185</v>
+        <v>1413218.17446921</v>
       </c>
       <c r="M10">
-        <v>4.202213462967589</v>
+        <v>592373.59144973</v>
       </c>
     </row>
     <row r="11">
@@ -4700,40 +8627,40 @@
         </is>
       </c>
       <c r="B11">
-        <v>5.617328680093157</v>
+        <v>665680.1854142901</v>
       </c>
       <c r="C11">
-        <v>42.01097016036041</v>
+        <v>9840.99486355</v>
       </c>
       <c r="D11">
-        <v>4.866108100912169</v>
+        <v>740990.41402314</v>
       </c>
       <c r="E11">
-        <v>15.36073003389004</v>
+        <v>43447.52711149</v>
       </c>
       <c r="F11">
-        <v>7.306480559277197</v>
+        <v>381490.97306181</v>
       </c>
       <c r="G11">
-        <v>3.330571371740546</v>
+        <v>991270.8746466</v>
       </c>
       <c r="H11">
-        <v>6.150036267523742</v>
+        <v>265322.50531427</v>
       </c>
       <c r="I11">
-        <v>11.17801266006694</v>
+        <v>85467.190158</v>
       </c>
       <c r="J11">
-        <v>10.65372514019709</v>
+        <v>98376.71669138</v>
       </c>
       <c r="K11">
-        <v>15.60645541401483</v>
+        <v>32121.68567442</v>
       </c>
       <c r="L11">
-        <v>2.636713873958467</v>
+        <v>1526403.94913186</v>
       </c>
       <c r="M11">
-        <v>4.483120963790372</v>
+        <v>556346.65185506</v>
       </c>
     </row>
     <row r="12">
@@ -4743,40 +8670,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.069195535210546</v>
+        <v>637733.03390839</v>
       </c>
       <c r="C12">
-        <v>35.2147888792215</v>
+        <v>11755.17209705</v>
       </c>
       <c r="D12">
-        <v>5.112226473547582</v>
+        <v>814021.82714716</v>
       </c>
       <c r="E12">
-        <v>12.82671598742309</v>
+        <v>44635.80454574</v>
       </c>
       <c r="F12">
-        <v>4.979943101935063</v>
+        <v>343547.58436562</v>
       </c>
       <c r="G12">
-        <v>4.036490703831773</v>
+        <v>1052430.5421023</v>
       </c>
       <c r="H12">
-        <v>6.387589466178004</v>
+        <v>277565.41846487</v>
       </c>
       <c r="I12">
-        <v>9.46650858416224</v>
+        <v>109682.8325342</v>
       </c>
       <c r="J12">
-        <v>9.574899684079915</v>
+        <v>91273.55021508</v>
       </c>
       <c r="K12">
-        <v>15.9356793561706</v>
+        <v>51530.6622661</v>
       </c>
       <c r="L12">
-        <v>2.600483862408256</v>
+        <v>1588211.03672875</v>
       </c>
       <c r="M12">
-        <v>5.068821687777465</v>
+        <v>588968.56462599</v>
       </c>
     </row>
     <row r="13">
@@ -4786,40 +8713,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>5.388413137518194</v>
+        <v>546655.96531675</v>
       </c>
       <c r="C13">
-        <v>65.75590486628836</v>
+        <v>13922.61242916</v>
       </c>
       <c r="D13">
-        <v>5.191104338740229</v>
+        <v>870508.52416386</v>
       </c>
       <c r="E13">
-        <v>15.61280053543057</v>
+        <v>38016.24984427</v>
       </c>
       <c r="F13">
-        <v>5.294222114664195</v>
+        <v>419485.01526537</v>
       </c>
       <c r="G13">
-        <v>3.269721774267901</v>
+        <v>1028348.42048615</v>
       </c>
       <c r="H13">
-        <v>6.275784981294243</v>
+        <v>273924.00893</v>
       </c>
       <c r="I13">
-        <v>9.636835208035075</v>
+        <v>108033.32910935</v>
       </c>
       <c r="J13">
-        <v>11.5398059414681</v>
+        <v>94196.92986552</v>
       </c>
       <c r="K13">
-        <v>13.3005123097336</v>
+        <v>48844.64989559</v>
       </c>
       <c r="L13">
-        <v>2.724262686460723</v>
+        <v>1706599.35500643</v>
       </c>
       <c r="M13">
-        <v>4.521622641837204</v>
+        <v>586543.71236765</v>
       </c>
     </row>
     <row r="14">
@@ -4829,40 +8756,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>5.583402427436035</v>
+        <v>542991.801428</v>
       </c>
       <c r="C14">
-        <v>34.09210194100303</v>
+        <v>6819.20627082</v>
       </c>
       <c r="D14">
-        <v>4.750967718405673</v>
+        <v>901364.50522174</v>
       </c>
       <c r="E14">
-        <v>14.24498141935839</v>
+        <v>38558.99277044</v>
       </c>
       <c r="F14">
-        <v>4.809642788510633</v>
+        <v>391716.48000284</v>
       </c>
       <c r="G14">
-        <v>2.647734586025055</v>
+        <v>1123305.95911595</v>
       </c>
       <c r="H14">
-        <v>5.702971315715192</v>
+        <v>319757.68717064</v>
       </c>
       <c r="I14">
-        <v>9.947187977501484</v>
+        <v>88676.52414736</v>
       </c>
       <c r="J14">
-        <v>11.1427385016287</v>
+        <v>88640.40897865999</v>
       </c>
       <c r="K14">
-        <v>13.32893244442354</v>
+        <v>57892.91403758</v>
       </c>
       <c r="L14">
-        <v>2.219495014628453</v>
+        <v>1705313.07232152</v>
       </c>
       <c r="M14">
-        <v>4.230148208989586</v>
+        <v>585683.36179405</v>
       </c>
     </row>
     <row r="15">
@@ -4872,40 +8799,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>2.801494740971123</v>
+        <v>1585846.57020404</v>
       </c>
       <c r="C15">
-        <v>21.42874699638312</v>
+        <v>15347.66460476</v>
       </c>
       <c r="D15">
-        <v>2.579167732812248</v>
+        <v>2668729.41172667</v>
       </c>
       <c r="E15">
-        <v>8.839013797088045</v>
+        <v>91052.46749138999</v>
       </c>
       <c r="F15">
-        <v>2.50396723498876</v>
+        <v>1129709.62575781</v>
       </c>
       <c r="G15">
-        <v>1.345952862980189</v>
+        <v>3235790.70906694</v>
       </c>
       <c r="H15">
-        <v>3.187451298122609</v>
+        <v>1010881.41394698</v>
       </c>
       <c r="I15">
-        <v>5.250948842459695</v>
+        <v>287717.91911227</v>
       </c>
       <c r="J15">
-        <v>5.047516493658409</v>
+        <v>328117.91186122</v>
       </c>
       <c r="K15">
-        <v>7.34276076077593</v>
+        <v>128510.44702868</v>
       </c>
       <c r="L15">
-        <v>1.2751156764505</v>
+        <v>5216852.63338819</v>
       </c>
       <c r="M15">
-        <v>2.218039121600745</v>
+        <v>1860794.59871368</v>
       </c>
     </row>
   </sheetData>
@@ -4992,40 +8919,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.761065154235808</v>
+        <v>31386173.55983117</v>
       </c>
       <c r="C2">
-        <v>25.0292155012763</v>
+        <v>591278.6211846001</v>
       </c>
       <c r="D2">
-        <v>4.316832306864735</v>
+        <v>39216322.22297917</v>
       </c>
       <c r="E2">
-        <v>12.75305920803599</v>
+        <v>2037827.12597768</v>
       </c>
       <c r="F2">
-        <v>4.535381916647462</v>
+        <v>16950178.69071486</v>
       </c>
       <c r="G2">
-        <v>3.183461575993505</v>
+        <v>41262944.44481871</v>
       </c>
       <c r="H2">
-        <v>4.920667992943769</v>
+        <v>13312754.30996443</v>
       </c>
       <c r="I2">
-        <v>9.486609230584248</v>
+        <v>2688703.40209015</v>
       </c>
       <c r="J2">
-        <v>9.748194755269294</v>
+        <v>2939515.22130755</v>
       </c>
       <c r="K2">
-        <v>14.65008531581546</v>
+        <v>1949733.22047878</v>
       </c>
       <c r="L2">
-        <v>2.659526969323039</v>
+        <v>51207826.75642961</v>
       </c>
       <c r="M2">
-        <v>4.281994401053494</v>
+        <v>19463370.07686919</v>
       </c>
     </row>
     <row r="3">
@@ -5035,40 +8962,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>4.957182608727809</v>
+        <v>29857166.10621455</v>
       </c>
       <c r="C3">
-        <v>25.48704840418356</v>
+        <v>583893.05360996</v>
       </c>
       <c r="D3">
-        <v>3.896687995659227</v>
+        <v>38823169.73967323</v>
       </c>
       <c r="E3">
-        <v>13.71775863007784</v>
+        <v>1553311.99999365</v>
       </c>
       <c r="F3">
-        <v>4.304315730717502</v>
+        <v>17163789.83674099</v>
       </c>
       <c r="G3">
-        <v>2.901481839858977</v>
+        <v>47746507.91634743</v>
       </c>
       <c r="H3">
-        <v>5.226533428955503</v>
+        <v>12828305.2255232</v>
       </c>
       <c r="I3">
-        <v>11.17785166900363</v>
+        <v>2506316.71976677</v>
       </c>
       <c r="J3">
-        <v>10.32294088359526</v>
+        <v>3300467.42812671</v>
       </c>
       <c r="K3">
-        <v>13.08765532395026</v>
+        <v>1953402.39969103</v>
       </c>
       <c r="L3">
-        <v>2.305669217386036</v>
+        <v>53373666.08407715</v>
       </c>
       <c r="M3">
-        <v>4.264477268327354</v>
+        <v>20449436.95807801</v>
       </c>
     </row>
     <row r="4">
@@ -5078,40 +9005,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>4.621107580910606</v>
+        <v>28492060.06861747</v>
       </c>
       <c r="C4">
-        <v>29.82501190121488</v>
+        <v>552665.41706172</v>
       </c>
       <c r="D4">
-        <v>4.50793563802797</v>
+        <v>38293698.09816235</v>
       </c>
       <c r="E4">
-        <v>12.40978692334551</v>
+        <v>1433081.03450745</v>
       </c>
       <c r="F4">
-        <v>4.745895638570152</v>
+        <v>16599255.30341888</v>
       </c>
       <c r="G4">
-        <v>2.953222413533885</v>
+        <v>43385088.33193519</v>
       </c>
       <c r="H4">
-        <v>5.054774190695815</v>
+        <v>11267282.08006066</v>
       </c>
       <c r="I4">
-        <v>9.281532773677794</v>
+        <v>2919678.4111142</v>
       </c>
       <c r="J4">
-        <v>11.6311173598268</v>
+        <v>2773167.47159966</v>
       </c>
       <c r="K4">
-        <v>15.8455879951145</v>
+        <v>1152664.79680251</v>
       </c>
       <c r="L4">
-        <v>2.306735260317303</v>
+        <v>58011188.40803067</v>
       </c>
       <c r="M4">
-        <v>4.0300941484044</v>
+        <v>20755839.44210238</v>
       </c>
     </row>
     <row r="5">
@@ -5121,40 +9048,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>4.634857059128383</v>
+        <v>28373994.15829523</v>
       </c>
       <c r="C5">
-        <v>26.16575446895731</v>
+        <v>801937.4915091801</v>
       </c>
       <c r="D5">
-        <v>3.749777259520345</v>
+        <v>37511157.05327562</v>
       </c>
       <c r="E5">
-        <v>11.67964185600136</v>
+        <v>2309964.58168535</v>
       </c>
       <c r="F5">
-        <v>4.811655836679517</v>
+        <v>15679994.10842191</v>
       </c>
       <c r="G5">
-        <v>3.322951907127385</v>
+        <v>44891029.51127592</v>
       </c>
       <c r="H5">
-        <v>5.849785552669916</v>
+        <v>11393693.58593425</v>
       </c>
       <c r="I5">
-        <v>11.95212818927324</v>
+        <v>3073256.22948613</v>
       </c>
       <c r="J5">
-        <v>9.857390207428294</v>
+        <v>3322931.13492816</v>
       </c>
       <c r="K5">
-        <v>17.89636076467712</v>
+        <v>1683056.8533818</v>
       </c>
       <c r="L5">
-        <v>2.326086332176682</v>
+        <v>57816272.9825268</v>
       </c>
       <c r="M5">
-        <v>4.501779466606551</v>
+        <v>21268125.09244174</v>
       </c>
     </row>
     <row r="6">
@@ -5164,40 +9091,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>6.021649254588031</v>
+        <v>29812925.29836671</v>
       </c>
       <c r="C6">
-        <v>33.412835739712</v>
+        <v>447738.22946172</v>
       </c>
       <c r="D6">
-        <v>3.72400295038999</v>
+        <v>35036154.07885488</v>
       </c>
       <c r="E6">
-        <v>14.80178281610042</v>
+        <v>2201094.36864728</v>
       </c>
       <c r="F6">
-        <v>4.796872579513805</v>
+        <v>16994551.50670693</v>
       </c>
       <c r="G6">
-        <v>3.23921203175561</v>
+        <v>42473073.82010518</v>
       </c>
       <c r="H6">
-        <v>5.572714938172997</v>
+        <v>11641658.26978083</v>
       </c>
       <c r="I6">
-        <v>11.18458352805767</v>
+        <v>2674415.2240157</v>
       </c>
       <c r="J6">
-        <v>9.168635134654707</v>
+        <v>3488347.18342805</v>
       </c>
       <c r="K6">
-        <v>14.06630639658684</v>
+        <v>1837840.31989806</v>
       </c>
       <c r="L6">
-        <v>2.614133774538237</v>
+        <v>57484631.84553381</v>
       </c>
       <c r="M6">
-        <v>4.250965283639797</v>
+        <v>20927855.61258717</v>
       </c>
     </row>
     <row r="7">
@@ -5207,40 +9134,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.200165653335199</v>
+        <v>26565430.22321526</v>
       </c>
       <c r="C7">
-        <v>33.47308059469479</v>
+        <v>515940.14938291</v>
       </c>
       <c r="D7">
-        <v>3.979482976268262</v>
+        <v>33804063.66021141</v>
       </c>
       <c r="E7">
-        <v>12.88120520212823</v>
+        <v>2454485.81309943</v>
       </c>
       <c r="F7">
-        <v>4.778564609248476</v>
+        <v>16024999.57884257</v>
       </c>
       <c r="G7">
-        <v>3.032694089882847</v>
+        <v>43011760.78430721</v>
       </c>
       <c r="H7">
-        <v>5.494229550988178</v>
+        <v>12801081.0435012</v>
       </c>
       <c r="I7">
-        <v>11.13833962074656</v>
+        <v>2491411.39060509</v>
       </c>
       <c r="J7">
-        <v>9.272177239913857</v>
+        <v>2919529.84291254</v>
       </c>
       <c r="K7">
-        <v>13.52834308261482</v>
+        <v>1681859.63974899</v>
       </c>
       <c r="L7">
-        <v>2.471672164495317</v>
+        <v>56962258.89310806</v>
       </c>
       <c r="M7">
-        <v>4.019885481486879</v>
+        <v>21450987.92563892</v>
       </c>
     </row>
     <row r="8">
@@ -5250,40 +9177,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.363176466552241</v>
+        <v>26139140.08185675</v>
       </c>
       <c r="C8">
-        <v>34.31415487961301</v>
+        <v>312782.39924022</v>
       </c>
       <c r="D8">
-        <v>4.688470857966046</v>
+        <v>33557233.23257538</v>
       </c>
       <c r="E8">
-        <v>16.30499578044843</v>
+        <v>1970235.90676037</v>
       </c>
       <c r="F8">
-        <v>5.110422414366949</v>
+        <v>16370742.52343315</v>
       </c>
       <c r="G8">
-        <v>3.672365440152794</v>
+        <v>41634100.23116716</v>
       </c>
       <c r="H8">
-        <v>5.991170298906833</v>
+        <v>12593573.24840604</v>
       </c>
       <c r="I8">
-        <v>12.15595501221395</v>
+        <v>2900703.17583832</v>
       </c>
       <c r="J8">
-        <v>11.32064196217064</v>
+        <v>2609106.22284488</v>
       </c>
       <c r="K8">
-        <v>14.88220183526882</v>
+        <v>1832729.91290518</v>
       </c>
       <c r="L8">
-        <v>2.591101795331353</v>
+        <v>58957111.55388619</v>
       </c>
       <c r="M8">
-        <v>3.858966305049048</v>
+        <v>21173754.26282011</v>
       </c>
     </row>
     <row r="9">
@@ -5293,40 +9220,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>5.471076149800356</v>
+        <v>25798951.48026295</v>
       </c>
       <c r="C9">
-        <v>34.50766685386222</v>
+        <v>480736.43602846</v>
       </c>
       <c r="D9">
-        <v>4.918904336987787</v>
+        <v>36150072.95056996</v>
       </c>
       <c r="E9">
-        <v>15.16787587509637</v>
+        <v>1502513.95328019</v>
       </c>
       <c r="F9">
-        <v>5.101313480870764</v>
+        <v>16182117.23424315</v>
       </c>
       <c r="G9">
-        <v>2.661810339996531</v>
+        <v>44249068.86657941</v>
       </c>
       <c r="H9">
-        <v>5.152264143100471</v>
+        <v>14013242.21456979</v>
       </c>
       <c r="I9">
-        <v>13.48845287999159</v>
+        <v>3964328.9695857</v>
       </c>
       <c r="J9">
-        <v>11.87420527310148</v>
+        <v>2708234.98070615</v>
       </c>
       <c r="K9">
-        <v>13.12917169011798</v>
+        <v>1632573.50642676</v>
       </c>
       <c r="L9">
-        <v>2.495904177774119</v>
+        <v>59282496.68696121</v>
       </c>
       <c r="M9">
-        <v>3.94283415826007</v>
+        <v>22734609.07914819</v>
       </c>
     </row>
     <row r="10">
@@ -5336,40 +9263,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>5.587799546579201</v>
+        <v>24432643.44338192</v>
       </c>
       <c r="C10">
-        <v>37.30930159780443</v>
+        <v>507839.30471653</v>
       </c>
       <c r="D10">
-        <v>4.792421814835913</v>
+        <v>32639274.53966394</v>
       </c>
       <c r="E10">
-        <v>15.8608760681409</v>
+        <v>1343342.80106139</v>
       </c>
       <c r="F10">
-        <v>5.757118915929259</v>
+        <v>13618520.09051506</v>
       </c>
       <c r="G10">
-        <v>3.695255613414222</v>
+        <v>40858633.9590264</v>
       </c>
       <c r="H10">
-        <v>5.301657297348373</v>
+        <v>13272543.93413581</v>
       </c>
       <c r="I10">
-        <v>11.07454314861207</v>
+        <v>3358464.31606831</v>
       </c>
       <c r="J10">
-        <v>11.88430211766331</v>
+        <v>2617903.50061816</v>
       </c>
       <c r="K10">
-        <v>14.01557586314087</v>
+        <v>1421522.8409979</v>
       </c>
       <c r="L10">
-        <v>2.566140000710484</v>
+        <v>51933159.62711499</v>
       </c>
       <c r="M10">
-        <v>4.440523157903022</v>
+        <v>21801536.84576209</v>
       </c>
     </row>
     <row r="11">
@@ -5379,40 +9306,40 @@
         </is>
       </c>
       <c r="B11">
-        <v>5.809145493335502</v>
+        <v>28786720.91794355</v>
       </c>
       <c r="C11">
-        <v>43.80568125499558</v>
+        <v>408254.61621266</v>
       </c>
       <c r="D11">
-        <v>4.969085789616813</v>
+        <v>30977914.13246308</v>
       </c>
       <c r="E11">
-        <v>15.49297970566271</v>
+        <v>1854287.12606593</v>
       </c>
       <c r="F11">
-        <v>7.277224933710413</v>
+        <v>15351812.85766153</v>
       </c>
       <c r="G11">
-        <v>3.466245561618275</v>
+        <v>41602758.74104248</v>
       </c>
       <c r="H11">
-        <v>6.450411929348247</v>
+        <v>11542246.58162419</v>
       </c>
       <c r="I11">
-        <v>11.22789640693645</v>
+        <v>3475801.14642303</v>
       </c>
       <c r="J11">
-        <v>10.8597827585541</v>
+        <v>3810303.43119425</v>
       </c>
       <c r="K11">
-        <v>16.3980337296549</v>
+        <v>1224811.39651429</v>
       </c>
       <c r="L11">
-        <v>2.943132364067676</v>
+        <v>56278517.89820383</v>
       </c>
       <c r="M11">
-        <v>4.692653728505976</v>
+        <v>20882197.58848391</v>
       </c>
     </row>
     <row r="12">
@@ -5422,40 +9349,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.400772953307841</v>
+        <v>27916320.27815214</v>
       </c>
       <c r="C12">
-        <v>36.4818423562836</v>
+        <v>551562.19400031</v>
       </c>
       <c r="D12">
-        <v>5.345867643625734</v>
+        <v>33411694.7300576</v>
       </c>
       <c r="E12">
-        <v>12.90947549484604</v>
+        <v>1804385.271303</v>
       </c>
       <c r="F12">
-        <v>5.032238671287409</v>
+        <v>14357304.96206663</v>
       </c>
       <c r="G12">
-        <v>4.13664047589622</v>
+        <v>44401028.18908073</v>
       </c>
       <c r="H12">
-        <v>7.182244898859302</v>
+        <v>12514294.85273337</v>
       </c>
       <c r="I12">
-        <v>9.808784210780406</v>
+        <v>4443179.24306939</v>
       </c>
       <c r="J12">
-        <v>9.943011077377713</v>
+        <v>3501158.00466761</v>
       </c>
       <c r="K12">
-        <v>16.15137409602901</v>
+        <v>2038776.81376374</v>
       </c>
       <c r="L12">
-        <v>2.851578477446991</v>
+        <v>59327622.5407189</v>
       </c>
       <c r="M12">
-        <v>5.153219264045873</v>
+        <v>21675442.78804322</v>
       </c>
     </row>
     <row r="13">
@@ -5465,40 +9392,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>5.718190489171315</v>
+        <v>24081266.93594478</v>
       </c>
       <c r="C13">
-        <v>65.93406161712177</v>
+        <v>581506.39036546</v>
       </c>
       <c r="D13">
-        <v>5.289902090111934</v>
+        <v>36215956.78207105</v>
       </c>
       <c r="E13">
-        <v>16.26397327374924</v>
+        <v>1546553.59283841</v>
       </c>
       <c r="F13">
-        <v>5.449984596186688</v>
+        <v>17033294.4622554</v>
       </c>
       <c r="G13">
-        <v>3.373588135764631</v>
+        <v>43589882.80908627</v>
       </c>
       <c r="H13">
-        <v>6.352815424207417</v>
+        <v>12120964.69039056</v>
       </c>
       <c r="I13">
-        <v>9.768602399824678</v>
+        <v>4456262.85362103</v>
       </c>
       <c r="J13">
-        <v>12.09580261445819</v>
+        <v>3667401.96064926</v>
       </c>
       <c r="K13">
-        <v>13.77444072706668</v>
+        <v>2093904.78849115</v>
       </c>
       <c r="L13">
-        <v>3.171578745563035</v>
+        <v>63659513.76324495</v>
       </c>
       <c r="M13">
-        <v>4.641905963685974</v>
+        <v>21513152.84583043</v>
       </c>
     </row>
     <row r="14">
@@ -5508,40 +9435,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>5.844957280733381</v>
+        <v>23957696.30456812</v>
       </c>
       <c r="C14">
-        <v>33.98088148304015</v>
+        <v>282032.59654772</v>
       </c>
       <c r="D14">
-        <v>4.784119523409654</v>
+        <v>37645002.71714141</v>
       </c>
       <c r="E14">
-        <v>14.23945280072857</v>
+        <v>1606232.63774442</v>
       </c>
       <c r="F14">
-        <v>4.863215881642399</v>
+        <v>16474106.02893549</v>
       </c>
       <c r="G14">
-        <v>2.731892140298864</v>
+        <v>47860408.40784301</v>
       </c>
       <c r="H14">
-        <v>5.840341338245266</v>
+        <v>14032929.92841926</v>
       </c>
       <c r="I14">
-        <v>10.03848469773556</v>
+        <v>3712319.31426991</v>
       </c>
       <c r="J14">
-        <v>11.50786873419352</v>
+        <v>3512275.56102429</v>
       </c>
       <c r="K14">
-        <v>13.88545510390364</v>
+        <v>2286336.23663922</v>
       </c>
       <c r="L14">
-        <v>2.523345525006838</v>
+        <v>63629970.7978253</v>
       </c>
       <c r="M14">
-        <v>4.399845424081461</v>
+        <v>21729915.2979905</v>
       </c>
     </row>
     <row r="15">
@@ -5551,40 +9478,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>3.011328764110506</v>
+        <v>67312471.68250692</v>
       </c>
       <c r="C15">
-        <v>21.23431533929238</v>
+        <v>636451.98036347</v>
       </c>
       <c r="D15">
-        <v>2.697276655180699</v>
+        <v>111153034.3045124</v>
       </c>
       <c r="E15">
-        <v>8.952906207330152</v>
+        <v>3793408.14984684</v>
       </c>
       <c r="F15">
-        <v>2.583946037826591</v>
+        <v>46317216.86544891</v>
       </c>
       <c r="G15">
-        <v>1.420415814524338</v>
+        <v>137466940.6872929</v>
       </c>
       <c r="H15">
-        <v>3.200656758911228</v>
+        <v>44063456.53773027</v>
       </c>
       <c r="I15">
-        <v>5.416464075623624</v>
+        <v>11748276.60620629</v>
       </c>
       <c r="J15">
-        <v>5.151044745511222</v>
+        <v>12983082.74811559</v>
       </c>
       <c r="K15">
-        <v>7.655651203388474</v>
+        <v>5275457.79206785</v>
       </c>
       <c r="L15">
-        <v>1.397619386001971</v>
+        <v>194790967.1894999</v>
       </c>
       <c r="M15">
-        <v>2.248346096069193</v>
+        <v>69090951.11796337</v>
       </c>
     </row>
   </sheetData>
@@ -5671,40 +9598,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.912697407505108</v>
+        <v>29406181.68651038</v>
       </c>
       <c r="C2">
-        <v>24.26319721906234</v>
+        <v>551664.06077882</v>
       </c>
       <c r="D2">
-        <v>4.324708906468424</v>
+        <v>36994345.37536697</v>
       </c>
       <c r="E2">
-        <v>13.10167594731925</v>
+        <v>1993194.91190328</v>
       </c>
       <c r="F2">
-        <v>4.578248455915082</v>
+        <v>15809047.04649692</v>
       </c>
       <c r="G2">
-        <v>3.295026471059417</v>
+        <v>40142492.38824281</v>
       </c>
       <c r="H2">
-        <v>5.038701133606147</v>
+        <v>12653952.36397054</v>
       </c>
       <c r="I2">
-        <v>9.522314864741229</v>
+        <v>2502586.28796718</v>
       </c>
       <c r="J2">
-        <v>9.928348139260574</v>
+        <v>2856112.53809865</v>
       </c>
       <c r="K2">
-        <v>14.99863910483803</v>
+        <v>1892619.95627188</v>
       </c>
       <c r="L2">
-        <v>2.693030461323722</v>
+        <v>48777180.86405141</v>
       </c>
       <c r="M2">
-        <v>4.605103800641801</v>
+        <v>18199861.1430582</v>
       </c>
     </row>
     <row r="3">
@@ -5714,40 +9641,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>5.014483328778505</v>
+        <v>28182302.54593618</v>
       </c>
       <c r="C3">
-        <v>26.16417452788204</v>
+        <v>564953.42384386</v>
       </c>
       <c r="D3">
-        <v>4.002567902248015</v>
+        <v>36557541.66646694</v>
       </c>
       <c r="E3">
-        <v>14.00338515513073</v>
+        <v>1524214.74965702</v>
       </c>
       <c r="F3">
-        <v>4.629792420371222</v>
+        <v>15937715.89306296</v>
       </c>
       <c r="G3">
-        <v>2.950679797993036</v>
+        <v>45965595.68838867</v>
       </c>
       <c r="H3">
-        <v>5.334776519471077</v>
+        <v>12364365.90520811</v>
       </c>
       <c r="I3">
-        <v>11.31081233467067</v>
+        <v>2432179.91910224</v>
       </c>
       <c r="J3">
-        <v>10.3917662704189</v>
+        <v>3232212.53585803</v>
       </c>
       <c r="K3">
-        <v>13.29439382398369</v>
+        <v>1911683.63524822</v>
       </c>
       <c r="L3">
-        <v>2.300810117863243</v>
+        <v>51082164.94347864</v>
       </c>
       <c r="M3">
-        <v>4.389893074446481</v>
+        <v>19067553.50293555</v>
       </c>
     </row>
     <row r="4">
@@ -5757,40 +9684,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>4.470786974789741</v>
+        <v>26607631.83504297</v>
       </c>
       <c r="C4">
-        <v>28.98870103292893</v>
+        <v>516326.78681654</v>
       </c>
       <c r="D4">
-        <v>4.678636783969589</v>
+        <v>36268021.83092315</v>
       </c>
       <c r="E4">
-        <v>12.37498889944348</v>
+        <v>1388146.87169589</v>
       </c>
       <c r="F4">
-        <v>4.891395253392661</v>
+        <v>15706132.9137405</v>
       </c>
       <c r="G4">
-        <v>2.976815242842345</v>
+        <v>42138829.22462219</v>
       </c>
       <c r="H4">
-        <v>5.265013684293117</v>
+        <v>11012189.9776826</v>
       </c>
       <c r="I4">
-        <v>9.263730531179588</v>
+        <v>2823008.6392941</v>
       </c>
       <c r="J4">
-        <v>11.73450010305552</v>
+        <v>2636651.65162974</v>
       </c>
       <c r="K4">
-        <v>15.90544844966313</v>
+        <v>1138788.46259419</v>
       </c>
       <c r="L4">
-        <v>2.333643161215545</v>
+        <v>55562425.42482335</v>
       </c>
       <c r="M4">
-        <v>4.072653547930511</v>
+        <v>18882440.72102164</v>
       </c>
     </row>
     <row r="5">
@@ -5800,40 +9727,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>4.838425839969454</v>
+        <v>27107398.61543223</v>
       </c>
       <c r="C5">
-        <v>26.48456461634016</v>
+        <v>819385.1483325401</v>
       </c>
       <c r="D5">
-        <v>3.802932611615216</v>
+        <v>34564008.43893124</v>
       </c>
       <c r="E5">
-        <v>12.12500102001515</v>
+        <v>2206215.45709012</v>
       </c>
       <c r="F5">
-        <v>4.994995154654816</v>
+        <v>14319348.72236363</v>
       </c>
       <c r="G5">
-        <v>3.410754002601589</v>
+        <v>43249540.93236996</v>
       </c>
       <c r="H5">
-        <v>5.9331028743417</v>
+        <v>10857586.52621619</v>
       </c>
       <c r="I5">
-        <v>11.96396060848642</v>
+        <v>3012205.01741223</v>
       </c>
       <c r="J5">
-        <v>9.670762267779347</v>
+        <v>3182751.11117553</v>
       </c>
       <c r="K5">
-        <v>18.49196791463107</v>
+        <v>1619002.78703555</v>
       </c>
       <c r="L5">
-        <v>2.296958030357034</v>
+        <v>55266969.90329797</v>
       </c>
       <c r="M5">
-        <v>4.649206943150784</v>
+        <v>19836173.6491016</v>
       </c>
     </row>
     <row r="6">
@@ -5843,40 +9770,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>6.127724198539114</v>
+        <v>28777670.10792583</v>
       </c>
       <c r="C6">
-        <v>35.733395846622</v>
+        <v>415516.41741292</v>
       </c>
       <c r="D6">
-        <v>3.676045052131931</v>
+        <v>32945502.8499626</v>
       </c>
       <c r="E6">
-        <v>15.4063203573333</v>
+        <v>2128887.8165323</v>
       </c>
       <c r="F6">
-        <v>4.834657960541141</v>
+        <v>15989175.02184598</v>
       </c>
       <c r="G6">
-        <v>3.286616611791349</v>
+        <v>40962628.90207746</v>
       </c>
       <c r="H6">
-        <v>5.805546688534231</v>
+        <v>11028622.1292907</v>
       </c>
       <c r="I6">
-        <v>11.41721538705517</v>
+        <v>2610485.46808286</v>
       </c>
       <c r="J6">
-        <v>9.365975305753109</v>
+        <v>3352824.61940406</v>
       </c>
       <c r="K6">
-        <v>14.60562559580327</v>
+        <v>1753043.85443104</v>
       </c>
       <c r="L6">
-        <v>2.685000823370979</v>
+        <v>55161996.06862786</v>
       </c>
       <c r="M6">
-        <v>4.543585077500088</v>
+        <v>19683545.82935353</v>
       </c>
     </row>
     <row r="7">
@@ -5886,40 +9813,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.109671004636389</v>
+        <v>25189104.66805541</v>
       </c>
       <c r="C7">
-        <v>33.84064069572609</v>
+        <v>504900.99154877</v>
       </c>
       <c r="D7">
-        <v>3.991906428720948</v>
+        <v>31753623.07130962</v>
       </c>
       <c r="E7">
-        <v>12.94071077033836</v>
+        <v>2410846.95547579</v>
       </c>
       <c r="F7">
-        <v>4.742444784461457</v>
+        <v>14838307.45369071</v>
       </c>
       <c r="G7">
-        <v>3.131622319326757</v>
+        <v>41324543.73821982</v>
       </c>
       <c r="H7">
-        <v>5.601988444042229</v>
+        <v>12144144.97658651</v>
       </c>
       <c r="I7">
-        <v>11.08277852050189</v>
+        <v>2385806.99413195</v>
       </c>
       <c r="J7">
-        <v>9.710836377306359</v>
+        <v>2770763.34782421</v>
       </c>
       <c r="K7">
-        <v>14.12512546779744</v>
+        <v>1529510.45737126</v>
       </c>
       <c r="L7">
-        <v>2.570691158554664</v>
+        <v>53834220.23265642</v>
       </c>
       <c r="M7">
-        <v>4.247708691501042</v>
+        <v>19898653.46792328</v>
       </c>
     </row>
     <row r="8">
@@ -5929,40 +9856,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.497627019202823</v>
+        <v>24805440.76481389</v>
       </c>
       <c r="C8">
-        <v>37.9825752239272</v>
+        <v>301704.40871468</v>
       </c>
       <c r="D8">
-        <v>4.649959312652776</v>
+        <v>31555589.01505932</v>
       </c>
       <c r="E8">
-        <v>16.43316690585362</v>
+        <v>1948473.86103908</v>
       </c>
       <c r="F8">
-        <v>5.013322003368592</v>
+        <v>14767279.56022402</v>
       </c>
       <c r="G8">
-        <v>3.683310428745417</v>
+        <v>39587132.58318329</v>
       </c>
       <c r="H8">
-        <v>6.161074058205409</v>
+        <v>12025605.86126311</v>
       </c>
       <c r="I8">
-        <v>12.50089467450232</v>
+        <v>2792746.98612934</v>
       </c>
       <c r="J8">
-        <v>11.53556713786412</v>
+        <v>2505941.07265778</v>
       </c>
       <c r="K8">
-        <v>15.66915297181068</v>
+        <v>1709334.00633857</v>
       </c>
       <c r="L8">
-        <v>2.67647079672481</v>
+        <v>56489751.98754588</v>
       </c>
       <c r="M8">
-        <v>4.099500745785307</v>
+        <v>19691498.593853</v>
       </c>
     </row>
     <row r="9">
@@ -5972,40 +9899,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>5.473630646850649</v>
+        <v>24575893.96503564</v>
       </c>
       <c r="C9">
-        <v>35.38185975543489</v>
+        <v>427521.71276834</v>
       </c>
       <c r="D9">
-        <v>4.740562057293507</v>
+        <v>34636711.45392877</v>
       </c>
       <c r="E9">
-        <v>15.33166491607292</v>
+        <v>1480850.00243658</v>
       </c>
       <c r="F9">
-        <v>5.026134120829043</v>
+        <v>15035326.65891444</v>
       </c>
       <c r="G9">
-        <v>2.724702668796694</v>
+        <v>42873456.77241577</v>
       </c>
       <c r="H9">
-        <v>5.172536716924252</v>
+        <v>13540707.89890188</v>
       </c>
       <c r="I9">
-        <v>13.84701907999673</v>
+        <v>3853180.30045248</v>
       </c>
       <c r="J9">
-        <v>12.11873855924429</v>
+        <v>2672312.66669606</v>
       </c>
       <c r="K9">
-        <v>13.16631858490031</v>
+        <v>1585357.76891209</v>
       </c>
       <c r="L9">
-        <v>2.583005870796699</v>
+        <v>57399932.23762121</v>
       </c>
       <c r="M9">
-        <v>4.147742048234455</v>
+        <v>21303775.33523442</v>
       </c>
     </row>
     <row r="10">
@@ -6015,40 +9942,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>5.641144705854895</v>
+        <v>23037443.62844466</v>
       </c>
       <c r="C10">
-        <v>34.83524320236246</v>
+        <v>416011.76746621</v>
       </c>
       <c r="D10">
-        <v>5.200067982106605</v>
+        <v>29120863.92627612</v>
       </c>
       <c r="E10">
-        <v>16.29218935927738</v>
+        <v>1269124.01096451</v>
       </c>
       <c r="F10">
-        <v>5.985658367415643</v>
+        <v>11595041.05200298</v>
       </c>
       <c r="G10">
-        <v>3.980013967455729</v>
+        <v>36820836.6707836</v>
       </c>
       <c r="H10">
-        <v>5.564384391020205</v>
+        <v>11695178.23873002</v>
       </c>
       <c r="I10">
-        <v>11.69508328536228</v>
+        <v>3157132.36007648</v>
       </c>
       <c r="J10">
-        <v>12.55284254328138</v>
+        <v>2420142.82861424</v>
       </c>
       <c r="K10">
-        <v>14.61299672977785</v>
+        <v>1279869.08970787</v>
       </c>
       <c r="L10">
-        <v>2.929827505064051</v>
+        <v>45215253.01957837</v>
       </c>
       <c r="M10">
-        <v>4.688353663582729</v>
+        <v>18523084.15147191</v>
       </c>
     </row>
     <row r="11">
@@ -6058,40 +9985,40 @@
         </is>
       </c>
       <c r="B11">
-        <v>5.648607258153838</v>
+        <v>27727646.82745574</v>
       </c>
       <c r="C11">
-        <v>46.71358432681334</v>
+        <v>354413.48121666</v>
       </c>
       <c r="D11">
-        <v>4.928767609922772</v>
+        <v>29396815.90226293</v>
       </c>
       <c r="E11">
-        <v>15.65703492833205</v>
+        <v>1851798.71908164</v>
       </c>
       <c r="F11">
-        <v>6.529238304965761</v>
+        <v>14092306.30972935</v>
       </c>
       <c r="G11">
-        <v>3.569319855262529</v>
+        <v>39786774.07404678</v>
       </c>
       <c r="H11">
-        <v>6.502361439390461</v>
+        <v>11019181.78049066</v>
       </c>
       <c r="I11">
-        <v>11.3030624773367</v>
+        <v>3403892.38812477</v>
       </c>
       <c r="J11">
-        <v>10.7031428721199</v>
+        <v>3678753.63909519</v>
       </c>
       <c r="K11">
-        <v>16.42905388632026</v>
+        <v>1163078.79529599</v>
       </c>
       <c r="L11">
-        <v>2.96242128932911</v>
+        <v>53445246.09253345</v>
       </c>
       <c r="M11">
-        <v>4.923114037997046</v>
+        <v>19567356.34172933</v>
       </c>
     </row>
     <row r="12">
@@ -6101,40 +10028,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.584098254169383</v>
+        <v>26958876.82610867</v>
       </c>
       <c r="C12">
-        <v>36.48974368933054</v>
+        <v>537857.70893691</v>
       </c>
       <c r="D12">
-        <v>5.488141924755609</v>
+        <v>31633626.9145492</v>
       </c>
       <c r="E12">
-        <v>13.45021647012651</v>
+        <v>1704169.162805</v>
       </c>
       <c r="F12">
-        <v>5.101462986777654</v>
+        <v>13453074.73888358</v>
       </c>
       <c r="G12">
-        <v>4.219002642104652</v>
+        <v>42828903.00355553</v>
       </c>
       <c r="H12">
-        <v>7.441023320204051</v>
+        <v>12027453.35240253</v>
       </c>
       <c r="I12">
-        <v>10.03896652086116</v>
+        <v>4284181.06076556</v>
       </c>
       <c r="J12">
-        <v>10.14347079410312</v>
+        <v>3366653.27749995</v>
       </c>
       <c r="K12">
-        <v>16.192072204311</v>
+        <v>2034337.39263772</v>
       </c>
       <c r="L12">
-        <v>2.928130514992404</v>
+        <v>56816530.2632226</v>
       </c>
       <c r="M12">
-        <v>5.394844538618257</v>
+        <v>20604696.40759467</v>
       </c>
     </row>
     <row r="13">
@@ -6144,40 +10071,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>5.776686894205137</v>
+        <v>23085061.0578944</v>
       </c>
       <c r="C13">
-        <v>75.25048096028368</v>
+        <v>538839.6565590199</v>
       </c>
       <c r="D13">
-        <v>5.232046297117255</v>
+        <v>34306767.62720327</v>
       </c>
       <c r="E13">
-        <v>16.71278699113314</v>
+        <v>1522317.45127395</v>
       </c>
       <c r="F13">
-        <v>5.634263718390546</v>
+        <v>16323603.24089517</v>
       </c>
       <c r="G13">
-        <v>3.523437546753659</v>
+        <v>42127290.2240188</v>
       </c>
       <c r="H13">
-        <v>6.644645930307025</v>
+        <v>11608307.36842683</v>
       </c>
       <c r="I13">
-        <v>9.978209334544404</v>
+        <v>4360334.20415541</v>
       </c>
       <c r="J13">
-        <v>12.46042443954272</v>
+        <v>3557685.63193113</v>
       </c>
       <c r="K13">
-        <v>14.02069282426549</v>
+        <v>1920133.87487908</v>
       </c>
       <c r="L13">
-        <v>3.217360206339153</v>
+        <v>60621576.82904702</v>
       </c>
       <c r="M13">
-        <v>4.906674989529294</v>
+        <v>20275070.86821482</v>
       </c>
     </row>
     <row r="14">
@@ -6187,40 +10114,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>5.97451466498412</v>
+        <v>22667984.18286439</v>
       </c>
       <c r="C14">
-        <v>33.98088148304015</v>
+        <v>282032.59654772</v>
       </c>
       <c r="D14">
-        <v>5.035548641296628</v>
+        <v>35506000.80098423</v>
       </c>
       <c r="E14">
-        <v>14.28856444721522</v>
+        <v>1553769.05865095</v>
       </c>
       <c r="F14">
-        <v>5.193453806876534</v>
+        <v>15443942.42787576</v>
       </c>
       <c r="G14">
-        <v>2.818735813056652</v>
+        <v>46220270.54167686</v>
       </c>
       <c r="H14">
-        <v>5.83247009819761</v>
+        <v>13315844.15609604</v>
       </c>
       <c r="I14">
-        <v>10.21303857353818</v>
+        <v>3554598.69631377</v>
       </c>
       <c r="J14">
-        <v>11.90502995804908</v>
+        <v>3349398.31297788</v>
       </c>
       <c r="K14">
-        <v>13.85482177154212</v>
+        <v>2212537.1964839</v>
       </c>
       <c r="L14">
-        <v>2.49604198472233</v>
+        <v>60203903.14185212</v>
       </c>
       <c r="M14">
-        <v>4.687344070489656</v>
+        <v>20184636.14206193</v>
       </c>
     </row>
     <row r="15">
@@ -6230,40 +10157,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>3.109225077734864</v>
+        <v>64327384.24417554</v>
       </c>
       <c r="C15">
-        <v>21.51441389611958</v>
+        <v>549135.17004091</v>
       </c>
       <c r="D15">
-        <v>2.685143945723477</v>
+        <v>106719910.3765618</v>
       </c>
       <c r="E15">
-        <v>9.026830989559883</v>
+        <v>3689604.51507628</v>
       </c>
       <c r="F15">
-        <v>2.699804897804296</v>
+        <v>44029615.1607125</v>
       </c>
       <c r="G15">
-        <v>1.466669716959992</v>
+        <v>132717924.6949092</v>
       </c>
       <c r="H15">
-        <v>3.234752121250274</v>
+        <v>42243905.89810163</v>
       </c>
       <c r="I15">
-        <v>5.525055130635562</v>
+        <v>11328279.31858741</v>
       </c>
       <c r="J15">
-        <v>5.309366948768028</v>
+        <v>12357102.80379633</v>
       </c>
       <c r="K15">
-        <v>7.798114314328378</v>
+        <v>5154961.04713042</v>
       </c>
       <c r="L15">
-        <v>1.434165225397692</v>
+        <v>187376291.512736</v>
       </c>
       <c r="M15">
-        <v>2.323109702251587</v>
+        <v>65256082.58050125</v>
       </c>
     </row>
   </sheetData>
@@ -6350,40 +10277,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>10.88403956732931</v>
+        <v>44865.81416728</v>
       </c>
       <c r="C2">
-        <v>97.95862972687051</v>
+        <v>595.63299924</v>
       </c>
       <c r="D2">
-        <v>20.48291298163564</v>
+        <v>13579.19759981</v>
       </c>
       <c r="E2">
-        <v>65.68328847628828</v>
+        <v>1134.14754132</v>
       </c>
       <c r="F2">
-        <v>25.47990644701036</v>
+        <v>8019.2560165</v>
       </c>
       <c r="G2">
-        <v>14.76037873131403</v>
+        <v>23756.15348941</v>
       </c>
       <c r="H2">
-        <v>27.33570893985508</v>
+        <v>8958.305337829999</v>
       </c>
       <c r="I2">
-        <v>34.45995225220212</v>
+        <v>3893.22335437</v>
       </c>
       <c r="J2">
-        <v>68.96494160734969</v>
+        <v>895.48157324</v>
       </c>
       <c r="K2">
-        <v>77.89564059170181</v>
+        <v>1233.5267968</v>
       </c>
       <c r="L2">
-        <v>8.266579299781277</v>
+        <v>84484.24312078999</v>
       </c>
       <c r="M2">
-        <v>13.78181371635161</v>
+        <v>45403.38566431</v>
       </c>
     </row>
     <row r="3">
@@ -6393,37 +10320,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>11.6724209837856</v>
+        <v>47085.99901669</v>
       </c>
       <c r="C3">
-        <v>72.4795144168605</v>
+        <v>583.84461237</v>
       </c>
       <c r="D3">
-        <v>19.63704327708712</v>
+        <v>15853.54919619</v>
       </c>
       <c r="F3">
-        <v>24.77687208223063</v>
+        <v>8741.055800169999</v>
       </c>
       <c r="G3">
-        <v>16.03491450719439</v>
+        <v>24549.14415362</v>
       </c>
       <c r="H3">
-        <v>25.08431355666757</v>
+        <v>8150.41873738</v>
       </c>
       <c r="I3">
-        <v>36.71374630752774</v>
+        <v>4850.91031507</v>
       </c>
       <c r="J3">
-        <v>43.74813813823339</v>
+        <v>3084.6519967</v>
       </c>
       <c r="K3">
-        <v>54.97424697707088</v>
+        <v>2647.89402193</v>
       </c>
       <c r="L3">
-        <v>7.633871457194735</v>
+        <v>114838.94415582</v>
       </c>
       <c r="M3">
-        <v>12.42194230886655</v>
+        <v>50195.41199763</v>
       </c>
     </row>
     <row r="4">
@@ -6433,37 +10360,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>11.34391467638396</v>
+        <v>43900.11952049</v>
       </c>
       <c r="C4">
-        <v>75.95697172487689</v>
+        <v>622.69557659</v>
       </c>
       <c r="D4">
-        <v>21.41399425332351</v>
+        <v>12931.54466897</v>
       </c>
       <c r="F4">
-        <v>21.52273184534238</v>
+        <v>11557.25625633</v>
       </c>
       <c r="G4">
-        <v>13.42694766356914</v>
+        <v>32328.41397373</v>
       </c>
       <c r="H4">
-        <v>27.64530225922303</v>
+        <v>8062.85538541</v>
       </c>
       <c r="I4">
-        <v>36.99147368692236</v>
+        <v>3337.73435612</v>
       </c>
       <c r="J4">
-        <v>61.33549998290628</v>
+        <v>777.6001092299999</v>
       </c>
       <c r="K4">
-        <v>52.89539115584287</v>
+        <v>1760.54460141</v>
       </c>
       <c r="L4">
-        <v>7.586709727342071</v>
+        <v>115766.54030916</v>
       </c>
       <c r="M4">
-        <v>11.34331007063474</v>
+        <v>51057.08810576</v>
       </c>
     </row>
     <row r="5">
@@ -6473,34 +10400,34 @@
         </is>
       </c>
       <c r="B5">
-        <v>11.3747842226693</v>
+        <v>50213.46599731</v>
       </c>
       <c r="D5">
-        <v>19.34989699386448</v>
+        <v>19531.02396868</v>
       </c>
       <c r="F5">
-        <v>24.94692922135104</v>
+        <v>7517.27559017</v>
       </c>
       <c r="G5">
-        <v>14.36963169826618</v>
+        <v>30470.26083798</v>
       </c>
       <c r="H5">
-        <v>28.27597948751253</v>
+        <v>7090.32299693</v>
       </c>
       <c r="I5">
-        <v>59.70136706181925</v>
+        <v>1857.06909712</v>
       </c>
       <c r="J5">
-        <v>75.25396990267464</v>
+        <v>730.4565896500001</v>
       </c>
       <c r="K5">
-        <v>73.63994600847651</v>
+        <v>853.7624083599999</v>
       </c>
       <c r="L5">
-        <v>9.649432885151224</v>
+        <v>105959.6990462</v>
       </c>
       <c r="M5">
-        <v>11.57271628771674</v>
+        <v>59230.08493636</v>
       </c>
     </row>
     <row r="6">
@@ -6510,37 +10437,37 @@
         </is>
       </c>
       <c r="B6">
-        <v>11.62816377011928</v>
+        <v>42002.43934282</v>
       </c>
       <c r="D6">
-        <v>21.46974308926088</v>
+        <v>12057.23569009</v>
       </c>
       <c r="E6">
-        <v>100.1133102715493</v>
+        <v>908.54267712</v>
       </c>
       <c r="F6">
-        <v>41.21891151220803</v>
+        <v>3212.48150231</v>
       </c>
       <c r="G6">
-        <v>18.57419183046546</v>
+        <v>17954.10682484</v>
       </c>
       <c r="H6">
-        <v>24.06790391691728</v>
+        <v>8860.459100460001</v>
       </c>
       <c r="I6">
-        <v>49.75759320722805</v>
+        <v>1615.37886527</v>
       </c>
       <c r="J6">
-        <v>106.692428108727</v>
+        <v>422.33827618</v>
       </c>
       <c r="K6">
-        <v>83.41589813453382</v>
+        <v>471.79285451</v>
       </c>
       <c r="L6">
-        <v>10.35046128337364</v>
+        <v>90531.27076956999</v>
       </c>
       <c r="M6">
-        <v>13.87824165591148</v>
+        <v>39546.41486495</v>
       </c>
     </row>
     <row r="7">
@@ -6550,34 +10477,34 @@
         </is>
       </c>
       <c r="B7">
-        <v>12.95947060585731</v>
+        <v>67354.43543668999</v>
       </c>
       <c r="D7">
-        <v>27.76181202134293</v>
+        <v>9240.136695380001</v>
       </c>
       <c r="F7">
-        <v>25.27502292619443</v>
+        <v>7813.92989587</v>
       </c>
       <c r="G7">
-        <v>13.66761652723121</v>
+        <v>25928.16954223</v>
       </c>
       <c r="H7">
-        <v>22.73429228823811</v>
+        <v>10687.00785953</v>
       </c>
       <c r="I7">
-        <v>52.74349959517398</v>
+        <v>1913.36242016</v>
       </c>
       <c r="J7">
-        <v>59.31532213932626</v>
+        <v>1074.17706304</v>
       </c>
       <c r="K7">
-        <v>48.10069610773503</v>
+        <v>1907.04065761</v>
       </c>
       <c r="L7">
-        <v>8.547235735092922</v>
+        <v>113186.75624591</v>
       </c>
       <c r="M7">
-        <v>13.82472557181569</v>
+        <v>38055.25302908</v>
       </c>
     </row>
     <row r="8">
@@ -6587,37 +10514,37 @@
         </is>
       </c>
       <c r="B8">
-        <v>13.18107422646523</v>
+        <v>55819.55830469</v>
       </c>
       <c r="D8">
-        <v>22.28752220455651</v>
+        <v>14135.68216444</v>
       </c>
       <c r="E8">
-        <v>99.85496843081762</v>
+        <v>581.63372192</v>
       </c>
       <c r="F8">
-        <v>24.52399659771746</v>
+        <v>11423.37428391</v>
       </c>
       <c r="G8">
-        <v>16.19789188166041</v>
+        <v>37258.53349684</v>
       </c>
       <c r="H8">
-        <v>21.06455160606996</v>
+        <v>9402.1810618</v>
       </c>
       <c r="I8">
-        <v>43.54310974008829</v>
+        <v>3406.8466178</v>
       </c>
       <c r="J8">
-        <v>74.59438748259728</v>
+        <v>1220.9703995</v>
       </c>
       <c r="K8">
-        <v>83.03927580549446</v>
+        <v>991.18349201</v>
       </c>
       <c r="L8">
-        <v>8.913550436737824</v>
+        <v>106332.51698632</v>
       </c>
       <c r="M8">
-        <v>13.04747503635194</v>
+        <v>37691.63369072</v>
       </c>
     </row>
     <row r="9">
@@ -6627,37 +10554,37 @@
         </is>
       </c>
       <c r="B9">
-        <v>14.2486398225663</v>
+        <v>55225.44167546</v>
       </c>
       <c r="C9">
-        <v>104.7498637518742</v>
+        <v>170.90309305</v>
       </c>
       <c r="D9">
-        <v>23.0869722334393</v>
+        <v>11524.06924892</v>
       </c>
       <c r="F9">
-        <v>30.57481579683628</v>
+        <v>5720.37337192</v>
       </c>
       <c r="G9">
-        <v>16.05515178672657</v>
+        <v>28162.5621921</v>
       </c>
       <c r="H9">
-        <v>29.10047426970458</v>
+        <v>8441.22835653</v>
       </c>
       <c r="I9">
-        <v>64.04001361320229</v>
+        <v>1696.48057743</v>
       </c>
       <c r="J9">
-        <v>48.72200412305921</v>
+        <v>1997.87347135</v>
       </c>
       <c r="K9">
-        <v>61.64399213813948</v>
+        <v>1178.10390405</v>
       </c>
       <c r="L9">
-        <v>8.322393034767737</v>
+        <v>121599.26146982</v>
       </c>
       <c r="M9">
-        <v>13.79733115023973</v>
+        <v>37603.56136762</v>
       </c>
     </row>
     <row r="10">
@@ -6667,34 +10594,34 @@
         </is>
       </c>
       <c r="B10">
-        <v>16.63314632266364</v>
+        <v>44576.29356951</v>
       </c>
       <c r="D10">
-        <v>29.0669930763188</v>
+        <v>7168.47525402</v>
       </c>
       <c r="F10">
-        <v>55.08833475185389</v>
+        <v>2238.68001786</v>
       </c>
       <c r="G10">
-        <v>25.18092250136463</v>
+        <v>14716.43030282</v>
       </c>
       <c r="H10">
-        <v>50.27050000914804</v>
+        <v>2070.79607497</v>
       </c>
       <c r="I10">
-        <v>53.76739997211524</v>
+        <v>3018.1151686</v>
       </c>
       <c r="J10">
-        <v>109.3373875642813</v>
+        <v>597.10621158</v>
       </c>
       <c r="K10">
-        <v>105.8182301671925</v>
+        <v>750.71611505</v>
       </c>
       <c r="L10">
-        <v>10.38945690122544</v>
+        <v>78018.59805304999</v>
       </c>
       <c r="M10">
-        <v>14.39507992235084</v>
+        <v>32739.22808547</v>
       </c>
     </row>
     <row r="11">
@@ -6704,37 +10631,37 @@
         </is>
       </c>
       <c r="B11">
-        <v>19.23032978552235</v>
+        <v>27165.43809992</v>
       </c>
       <c r="C11">
-        <v>106.3607346536877</v>
+        <v>457.67065491</v>
       </c>
       <c r="D11">
-        <v>28.46718368645864</v>
+        <v>8260.908885749999</v>
       </c>
       <c r="F11">
-        <v>43.04452963359602</v>
+        <v>5286.61108609</v>
       </c>
       <c r="G11">
-        <v>27.72774884392102</v>
+        <v>21043.73798484</v>
       </c>
       <c r="H11">
-        <v>38.57558909172776</v>
+        <v>5290.44164979</v>
       </c>
       <c r="I11">
-        <v>60.15276779950683</v>
+        <v>3542.47787025</v>
       </c>
       <c r="J11">
-        <v>93.7459183343129</v>
+        <v>335.58599604</v>
       </c>
       <c r="K11">
-        <v>74.9661352227926</v>
+        <v>1499.39015131</v>
       </c>
       <c r="L11">
-        <v>14.30863576736613</v>
+        <v>67712.92236000999</v>
       </c>
       <c r="M11">
-        <v>18.89715525346656</v>
+        <v>29124.1332089</v>
       </c>
     </row>
     <row r="12">
@@ -6744,37 +10671,37 @@
         </is>
       </c>
       <c r="B12">
-        <v>23.00765219995634</v>
+        <v>39059.67151178</v>
       </c>
       <c r="C12">
-        <v>104.2658975484439</v>
+        <v>174.73897293</v>
       </c>
       <c r="D12">
-        <v>32.11655720962137</v>
+        <v>8724.40828023</v>
       </c>
       <c r="F12">
-        <v>48.65564042170303</v>
+        <v>5218.4548039</v>
       </c>
       <c r="G12">
-        <v>18.69969766841804</v>
+        <v>27334.14322387</v>
       </c>
       <c r="H12">
-        <v>37.06520248493438</v>
+        <v>7463.13156473</v>
       </c>
       <c r="I12">
-        <v>38.55987763448275</v>
+        <v>5720.6252526</v>
       </c>
       <c r="J12">
-        <v>51.19653117965146</v>
+        <v>2819.74298542</v>
       </c>
       <c r="K12">
-        <v>48.36449293923646</v>
+        <v>2786.28197115</v>
       </c>
       <c r="L12">
-        <v>9.79262047423582</v>
+        <v>81369.95049389001</v>
       </c>
       <c r="M12">
-        <v>16.01610380572933</v>
+        <v>40639.25023177</v>
       </c>
     </row>
     <row r="13">
@@ -6784,37 +10711,37 @@
         </is>
       </c>
       <c r="B13">
-        <v>16.96573346064504</v>
+        <v>32707.499524</v>
       </c>
       <c r="D13">
-        <v>25.19079835699459</v>
+        <v>11191.24476329</v>
       </c>
       <c r="E13">
-        <v>74.69885068585307</v>
+        <v>1040.21771394</v>
       </c>
       <c r="F13">
-        <v>29.97041284958615</v>
+        <v>7150.67094858</v>
       </c>
       <c r="G13">
-        <v>17.48662802167587</v>
+        <v>21759.78373378</v>
       </c>
       <c r="H13">
-        <v>25.24071411037167</v>
+        <v>11811.77089935</v>
       </c>
       <c r="I13">
-        <v>45.30822072482657</v>
+        <v>5448.66684699</v>
       </c>
       <c r="J13">
-        <v>39.92486207426452</v>
+        <v>3739.1547928</v>
       </c>
       <c r="K13">
-        <v>93.51873053818154</v>
+        <v>343.83544956</v>
       </c>
       <c r="L13">
-        <v>9.858174161410171</v>
+        <v>123861.14610292</v>
       </c>
       <c r="M13">
-        <v>26.26350893437704</v>
+        <v>30022.54432087</v>
       </c>
     </row>
     <row r="14">
@@ -6824,37 +10751,37 @@
         </is>
       </c>
       <c r="B14">
-        <v>16.00738646197612</v>
+        <v>35598.82668519</v>
       </c>
       <c r="D14">
-        <v>22.91298956339881</v>
+        <v>15764.49230674</v>
       </c>
       <c r="E14">
-        <v>70.34402702576243</v>
+        <v>1072.64153558</v>
       </c>
       <c r="F14">
-        <v>30.88895958590369</v>
+        <v>6720.92226263</v>
       </c>
       <c r="G14">
-        <v>18.66247798767978</v>
+        <v>36230.35545924</v>
       </c>
       <c r="H14">
-        <v>22.16634046368916</v>
+        <v>17356.76048435</v>
       </c>
       <c r="I14">
-        <v>41.41763978466046</v>
+        <v>6895.8168384</v>
       </c>
       <c r="J14">
-        <v>49.43776467894947</v>
+        <v>3458.58657059</v>
       </c>
       <c r="K14">
-        <v>47.20304766192323</v>
+        <v>2691.575031</v>
       </c>
       <c r="L14">
-        <v>9.135358801745452</v>
+        <v>127185.58821585</v>
       </c>
       <c r="M14">
-        <v>15.49094013565183</v>
+        <v>36174.99700035</v>
       </c>
     </row>
     <row r="15">
@@ -6864,34 +10791,34 @@
         </is>
       </c>
       <c r="B15">
-        <v>8.440816389719373</v>
+        <v>112176.03868358</v>
       </c>
       <c r="D15">
-        <v>16.69240848621936</v>
+        <v>27920.73408712</v>
       </c>
       <c r="F15">
-        <v>19.36705595780691</v>
+        <v>18513.20276421</v>
       </c>
       <c r="G15">
-        <v>9.53087037809791</v>
+        <v>74202.35635133</v>
       </c>
       <c r="H15">
-        <v>13.00723158608827</v>
+        <v>33499.51116839</v>
       </c>
       <c r="I15">
-        <v>16.85336664081954</v>
+        <v>16680.98747064</v>
       </c>
       <c r="J15">
-        <v>44.38849190150099</v>
+        <v>2892.73850481</v>
       </c>
       <c r="K15">
-        <v>25.04653487984018</v>
+        <v>12364.15048422</v>
       </c>
       <c r="L15">
-        <v>4.822720847207865</v>
+        <v>371535.93561262</v>
       </c>
       <c r="M15">
-        <v>7.884149019229858</v>
+        <v>124056.13380581</v>
       </c>
     </row>
   </sheetData>
@@ -6978,40 +10905,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>13.06051970588445</v>
+        <v>666572.2465374001</v>
       </c>
       <c r="C2">
-        <v>97.95862972687053</v>
+        <v>10721.39398632</v>
       </c>
       <c r="D2">
-        <v>25.00257056552407</v>
+        <v>225132.43250087</v>
       </c>
       <c r="E2">
-        <v>66.05895387138429</v>
+        <v>13930.08508954</v>
       </c>
       <c r="F2">
-        <v>35.64091798002088</v>
+        <v>131839.36280077</v>
       </c>
       <c r="G2">
-        <v>20.59143742420957</v>
+        <v>289756.29552556</v>
       </c>
       <c r="H2">
-        <v>32.24918674553307</v>
+        <v>134630.13526001</v>
       </c>
       <c r="I2">
-        <v>49.09199329211687</v>
+        <v>60607.36486665</v>
       </c>
       <c r="J2">
-        <v>71.54848095867294</v>
+        <v>25533.47632362</v>
       </c>
       <c r="K2">
-        <v>77.03201414857267</v>
+        <v>25578.8187439</v>
       </c>
       <c r="L2">
-        <v>9.463035311910666</v>
+        <v>1388023.09968044</v>
       </c>
       <c r="M2">
-        <v>13.96895799631572</v>
+        <v>864724.85622401</v>
       </c>
     </row>
     <row r="3">
@@ -7021,37 +10948,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>13.37468161767797</v>
+        <v>850148.8477376</v>
       </c>
       <c r="C3">
-        <v>68.9335915012973</v>
+        <v>10082.10465552</v>
       </c>
       <c r="D3">
-        <v>21.32562679043168</v>
+        <v>224333.837643</v>
       </c>
       <c r="F3">
-        <v>33.68418159384515</v>
+        <v>170866.00922546</v>
       </c>
       <c r="G3">
-        <v>17.78121104513171</v>
+        <v>338699.30829528</v>
       </c>
       <c r="H3">
-        <v>29.06632009619359</v>
+        <v>118915.5670959</v>
       </c>
       <c r="I3">
-        <v>41.87702928846286</v>
+        <v>75158.03351896</v>
       </c>
       <c r="J3">
-        <v>49.12777645930105</v>
+        <v>34504.85934592</v>
       </c>
       <c r="K3">
-        <v>53.99543054435556</v>
+        <v>47587.546159</v>
       </c>
       <c r="L3">
-        <v>9.212745108200798</v>
+        <v>1742558.49527814</v>
       </c>
       <c r="M3">
-        <v>13.02079510607365</v>
+        <v>899751.41083021</v>
       </c>
     </row>
     <row r="4">
@@ -7061,37 +10988,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>13.14515343095321</v>
+        <v>666457.5710363</v>
       </c>
       <c r="C4">
-        <v>82.745847062506</v>
+        <v>2780.50693607</v>
       </c>
       <c r="D4">
-        <v>25.79257114956959</v>
+        <v>217243.61110671</v>
       </c>
       <c r="F4">
-        <v>24.86923989826635</v>
+        <v>230836.28595987</v>
       </c>
       <c r="G4">
-        <v>17.28486777385459</v>
+        <v>465752.58749005</v>
       </c>
       <c r="H4">
-        <v>30.00876813908369</v>
+        <v>143354.61619409</v>
       </c>
       <c r="I4">
-        <v>52.28030652607627</v>
+        <v>47289.08975739</v>
       </c>
       <c r="J4">
-        <v>61.22180927521831</v>
+        <v>9955.200820779999</v>
       </c>
       <c r="K4">
-        <v>52.38372423042475</v>
+        <v>55523.1044049</v>
       </c>
       <c r="L4">
-        <v>8.83832827370429</v>
+        <v>1712612.11264376</v>
       </c>
       <c r="M4">
-        <v>12.04928587504501</v>
+        <v>1010415.36730785</v>
       </c>
     </row>
     <row r="5">
@@ -7101,34 +11028,34 @@
         </is>
       </c>
       <c r="B5">
-        <v>12.2745773291146</v>
+        <v>782533.65017358</v>
       </c>
       <c r="D5">
-        <v>21.46661892468845</v>
+        <v>221893.50192605</v>
       </c>
       <c r="F5">
-        <v>27.06045415055887</v>
+        <v>147011.89771075</v>
       </c>
       <c r="G5">
-        <v>16.14617953333519</v>
+        <v>485297.47871318</v>
       </c>
       <c r="H5">
-        <v>32.59580203318911</v>
+        <v>125655.65116034</v>
       </c>
       <c r="I5">
-        <v>69.34911796257366</v>
+        <v>13833.60064455</v>
       </c>
       <c r="J5">
-        <v>78.23643978954827</v>
+        <v>13161.09105555</v>
       </c>
       <c r="K5">
-        <v>75.92367603949015</v>
+        <v>6085.411116019999</v>
       </c>
       <c r="L5">
-        <v>10.11219064354203</v>
+        <v>1517241.87530838</v>
       </c>
       <c r="M5">
-        <v>11.38515437738278</v>
+        <v>1056577.92738027</v>
       </c>
     </row>
     <row r="6">
@@ -7138,37 +11065,37 @@
         </is>
       </c>
       <c r="B6">
-        <v>12.74656310213323</v>
+        <v>702344.50298054</v>
       </c>
       <c r="D6">
-        <v>23.02492222770072</v>
+        <v>183667.05339051</v>
       </c>
       <c r="E6">
-        <v>100.1133102715493</v>
+        <v>6359.79873984</v>
       </c>
       <c r="F6">
-        <v>41.91171039075667</v>
+        <v>47472.6188405</v>
       </c>
       <c r="G6">
-        <v>21.98183721864885</v>
+        <v>265738.24566367</v>
       </c>
       <c r="H6">
-        <v>25.82523050447608</v>
+        <v>147113.36351632</v>
       </c>
       <c r="I6">
-        <v>48.89747612034444</v>
+        <v>23163.20724464</v>
       </c>
       <c r="J6">
-        <v>106.692428108727</v>
+        <v>4223.3827618</v>
       </c>
       <c r="K6">
-        <v>87.0297639872767</v>
+        <v>8996.764264450001</v>
       </c>
       <c r="L6">
-        <v>11.98875771414853</v>
+        <v>1295824.64563804</v>
       </c>
       <c r="M6">
-        <v>14.13466916119175</v>
+        <v>801415.04470877</v>
       </c>
     </row>
     <row r="7">
@@ -7178,34 +11105,34 @@
         </is>
       </c>
       <c r="B7">
-        <v>14.81770870041462</v>
+        <v>1070698.87353972</v>
       </c>
       <c r="D7">
-        <v>30.54495004728628</v>
+        <v>112030.32449808</v>
       </c>
       <c r="F7">
-        <v>31.56860274874189</v>
+        <v>146094.94174061</v>
       </c>
       <c r="G7">
-        <v>16.41977054771604</v>
+        <v>365041.35281516</v>
       </c>
       <c r="H7">
-        <v>26.54741790706277</v>
+        <v>236541.05297348</v>
       </c>
       <c r="I7">
-        <v>51.47577828481194</v>
+        <v>41494.25900098</v>
       </c>
       <c r="J7">
-        <v>62.15024840332354</v>
+        <v>6621.19771546</v>
       </c>
       <c r="K7">
-        <v>57.97228105723156</v>
+        <v>35717.85502889</v>
       </c>
       <c r="L7">
-        <v>8.761283788599993</v>
+        <v>1686246.18316794</v>
       </c>
       <c r="M7">
-        <v>15.3907518723124</v>
+        <v>740505.41473417</v>
       </c>
     </row>
     <row r="8">
@@ -7215,37 +11142,37 @@
         </is>
       </c>
       <c r="B8">
-        <v>13.53898433370722</v>
+        <v>886566.4765217</v>
       </c>
       <c r="D8">
-        <v>25.06408399696877</v>
+        <v>213263.56832598</v>
       </c>
       <c r="E8">
-        <v>99.85496843081762</v>
+        <v>6979.60466304</v>
       </c>
       <c r="F8">
-        <v>25.22819328482898</v>
+        <v>187952.90506413</v>
       </c>
       <c r="G8">
-        <v>20.13340423463137</v>
+        <v>561178.13852454</v>
       </c>
       <c r="H8">
-        <v>22.43710391110071</v>
+        <v>170104.4826053</v>
       </c>
       <c r="I8">
-        <v>49.54007534864434</v>
+        <v>30452.24189459</v>
       </c>
       <c r="J8">
-        <v>84.97712547020704</v>
+        <v>4881.9654019</v>
       </c>
       <c r="K8">
-        <v>89.613101948579</v>
+        <v>18383.9978713</v>
       </c>
       <c r="L8">
-        <v>10.29943318945102</v>
+        <v>1579318.35102105</v>
       </c>
       <c r="M8">
-        <v>12.94608428859329</v>
+        <v>741771.6655864801</v>
       </c>
     </row>
     <row r="9">
@@ -7255,37 +11182,37 @@
         </is>
       </c>
       <c r="B9">
-        <v>15.50812454604493</v>
+        <v>906117.429735</v>
       </c>
       <c r="C9">
-        <v>104.7498637518742</v>
+        <v>1709.0309305</v>
       </c>
       <c r="D9">
-        <v>28.03223635036953</v>
+        <v>184589.41017338</v>
       </c>
       <c r="F9">
-        <v>35.90187368255865</v>
+        <v>93760.66951820999</v>
       </c>
       <c r="G9">
-        <v>22.05341313647074</v>
+        <v>408868.00033361</v>
       </c>
       <c r="H9">
-        <v>33.90330672705551</v>
+        <v>126008.7752829</v>
       </c>
       <c r="I9">
-        <v>66.2861768793632</v>
+        <v>40033.3017117</v>
       </c>
       <c r="J9">
-        <v>49.98857317123316</v>
+        <v>31296.12663786</v>
       </c>
       <c r="K9">
-        <v>61.05350137975564</v>
+        <v>25166.0217987</v>
       </c>
       <c r="L9">
-        <v>9.171288024654075</v>
+        <v>1701863.77381794</v>
       </c>
       <c r="M9">
-        <v>14.47667379156451</v>
+        <v>727643.190065</v>
       </c>
     </row>
     <row r="10">
@@ -7295,34 +11222,34 @@
         </is>
       </c>
       <c r="B10">
-        <v>18.31411642524297</v>
+        <v>780210.78958353</v>
       </c>
       <c r="D10">
-        <v>32.04783984037337</v>
+        <v>80977.97326023001</v>
       </c>
       <c r="F10">
-        <v>56.52264821518372</v>
+        <v>53460.78271535</v>
       </c>
       <c r="G10">
-        <v>24.9585696410692</v>
+        <v>180282.67792225</v>
       </c>
       <c r="H10">
-        <v>47.71431862830468</v>
+        <v>30356.35034206</v>
       </c>
       <c r="I10">
-        <v>59.42989459401725</v>
+        <v>57808.96041389</v>
       </c>
       <c r="J10">
-        <v>109.3373875642813</v>
+        <v>5971.0621158</v>
       </c>
       <c r="K10">
-        <v>105.8182301671926</v>
+        <v>15014.322301</v>
       </c>
       <c r="L10">
-        <v>11.88932176602197</v>
+        <v>1231026.30249328</v>
       </c>
       <c r="M10">
-        <v>14.55610469781471</v>
+        <v>661097.6594761</v>
       </c>
     </row>
     <row r="11">
@@ -7332,37 +11259,37 @@
         </is>
       </c>
       <c r="B11">
-        <v>18.71038870160313</v>
+        <v>425122.76651073</v>
       </c>
       <c r="C11">
-        <v>106.3607346536877</v>
+        <v>9153.413098200001</v>
       </c>
       <c r="D11">
-        <v>31.08408675778152</v>
+        <v>101941.78063607</v>
       </c>
       <c r="F11">
-        <v>45.22232126995625</v>
+        <v>96496.59536002</v>
       </c>
       <c r="G11">
-        <v>44.47102247075268</v>
+        <v>424813.69084408</v>
       </c>
       <c r="H11">
-        <v>37.49891868290691</v>
+        <v>65375.85774521</v>
       </c>
       <c r="I11">
-        <v>66.11517146988412</v>
+        <v>72477.73591592</v>
       </c>
       <c r="J11">
-        <v>93.7459183343129</v>
+        <v>6711.7199208</v>
       </c>
       <c r="K11">
-        <v>86.70577884642732</v>
+        <v>9144.233225260001</v>
       </c>
       <c r="L11">
-        <v>15.64621366980357</v>
+        <v>992661.74428112</v>
       </c>
       <c r="M11">
-        <v>18.77344420130546</v>
+        <v>629499.39529298</v>
       </c>
     </row>
     <row r="12">
@@ -7372,37 +11299,37 @@
         </is>
       </c>
       <c r="B12">
-        <v>20.23048273003948</v>
+        <v>618125.8354027</v>
       </c>
       <c r="C12">
-        <v>104.2658975484439</v>
+        <v>4717.95226911</v>
       </c>
       <c r="D12">
-        <v>34.29137684446297</v>
+        <v>144855.90352286</v>
       </c>
       <c r="F12">
-        <v>46.90843502269945</v>
+        <v>62961.7413653</v>
       </c>
       <c r="G12">
-        <v>24.23651756014295</v>
+        <v>387335.19971241</v>
       </c>
       <c r="H12">
-        <v>40.85751408390479</v>
+        <v>130606.54024695</v>
       </c>
       <c r="I12">
-        <v>42.31890966376575</v>
+        <v>99958.12481661</v>
       </c>
       <c r="J12">
-        <v>58.93130561258408</v>
+        <v>22927.27952782</v>
       </c>
       <c r="K12">
-        <v>48.78844178841195</v>
+        <v>50575.2773875</v>
       </c>
       <c r="L12">
-        <v>12.2163648626533</v>
+        <v>1195883.93041618</v>
       </c>
       <c r="M12">
-        <v>16.76013090781447</v>
+        <v>722607.99605344</v>
       </c>
     </row>
     <row r="13">
@@ -7412,37 +11339,37 @@
         </is>
       </c>
       <c r="B13">
-        <v>17.6542153685519</v>
+        <v>560925.10991627</v>
       </c>
       <c r="D13">
-        <v>26.25250325439025</v>
+        <v>169804.21051088</v>
       </c>
       <c r="E13">
-        <v>82.44927181896281</v>
+        <v>15144.07806192</v>
       </c>
       <c r="F13">
-        <v>31.89286702374839</v>
+        <v>101874.42903878</v>
       </c>
       <c r="G13">
-        <v>19.59193698768939</v>
+        <v>354680.62328842</v>
       </c>
       <c r="H13">
-        <v>27.76884603547233</v>
+        <v>216348.45319323</v>
       </c>
       <c r="I13">
-        <v>52.01937279490553</v>
+        <v>124596.78967325</v>
       </c>
       <c r="J13">
-        <v>46.71102848187128</v>
+        <v>67908.35641492999</v>
       </c>
       <c r="K13">
-        <v>93.51873053818156</v>
+        <v>5157.5317434</v>
       </c>
       <c r="L13">
-        <v>10.99422156897608</v>
+        <v>1859073.62167098</v>
       </c>
       <c r="M13">
-        <v>26.32878128729407</v>
+        <v>625436.7292404399</v>
       </c>
     </row>
     <row r="14">
@@ -7452,37 +11379,37 @@
         </is>
       </c>
       <c r="B14">
-        <v>19.22271996217058</v>
+        <v>595491.86357025</v>
       </c>
       <c r="D14">
-        <v>21.86771518390527</v>
+        <v>239307.59681731</v>
       </c>
       <c r="E14">
-        <v>70.34402702576244</v>
+        <v>21452.8307116</v>
       </c>
       <c r="F14">
-        <v>39.28430716403046</v>
+        <v>128503.34751557</v>
       </c>
       <c r="G14">
-        <v>21.16133103132719</v>
+        <v>576983.00260953</v>
       </c>
       <c r="H14">
-        <v>21.66179640470497</v>
+        <v>257343.77668794</v>
       </c>
       <c r="I14">
-        <v>43.04628211236439</v>
+        <v>138080.62127203</v>
       </c>
       <c r="J14">
-        <v>79.98212423910587</v>
+        <v>75246.25260681</v>
       </c>
       <c r="K14">
-        <v>50.78443051047075</v>
+        <v>43391.5429104</v>
       </c>
       <c r="L14">
-        <v>10.91855095760117</v>
+        <v>1982801.70487574</v>
       </c>
       <c r="M14">
-        <v>18.4440931058484</v>
+        <v>820937.50982482</v>
       </c>
     </row>
     <row r="15">
@@ -7492,34 +11419,34 @@
         </is>
       </c>
       <c r="B15">
-        <v>9.69149621992819</v>
+        <v>1830829.94359026</v>
       </c>
       <c r="D15">
-        <v>18.37969917316634</v>
+        <v>492220.08924118</v>
       </c>
       <c r="F15">
-        <v>20.76907996618045</v>
+        <v>322398.39274928</v>
       </c>
       <c r="G15">
-        <v>11.35897230358814</v>
+        <v>1290035.31888421</v>
       </c>
       <c r="H15">
-        <v>13.6970897488896</v>
+        <v>585968.10883834</v>
       </c>
       <c r="I15">
-        <v>18.20209026058754</v>
+        <v>277342.86872456</v>
       </c>
       <c r="J15">
-        <v>65.74269057249249</v>
+        <v>36522.58701203</v>
       </c>
       <c r="K15">
-        <v>22.98513217862763</v>
+        <v>156770.16987371</v>
       </c>
       <c r="L15">
-        <v>5.819586513418102</v>
+        <v>5881671.69644798</v>
       </c>
       <c r="M15">
-        <v>8.832909239354489</v>
+        <v>2400084.96342771</v>
       </c>
     </row>
   </sheetData>
